--- a/output/一级导线观测手簿.xlsx
+++ b/output/一级导线观测手簿.xlsx
@@ -621,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -630,7 +630,7 @@
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -679,7 +679,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>233°10'18.0"</t>
+          <t>180°02'29.3"</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>53°07'48.3"</t>
+          <t>359°59'58.7"</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53°10'18.5"</t>
+          <t>0°02'28.1"</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>53°07'48.3"</t>
+          <t>359°59'58.7"</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -767,7 +767,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -777,29 +777,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>57°01'04.5"</t>
+          <t>53°10'20.0"</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>56°58'34.0"</t>
+          <t>53°07'50.4"</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3°50'45.7"</t>
+          <t>53°07'51.6"</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -817,29 +817,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>237°01'03.4"</t>
+          <t>233°10'20.8"</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>56°58'34.0"</t>
+          <t>53°07'50.4"</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3°50'45.7"</t>
+          <t>53°07'51.6"</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>323°10'19.3"</t>
+          <t>270°02'31.1"</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>53°07'48.5"</t>
+          <t>0°00'00.3"</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>143°10'17.7"</t>
+          <t>90°02'29.5"</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>53°07'48.5"</t>
+          <t>0°00'00.3"</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -927,7 +927,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -937,29 +937,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>147°01'04.3"</t>
+          <t>143°10'19.8"</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>56°58'34.2"</t>
+          <t>53°07'49.2"</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3°50'45.7"</t>
+          <t>53°07'48.9"</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -977,29 +977,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>327°01'04.1"</t>
+          <t>323°10'18.6"</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>56°58'34.2"</t>
+          <t>53°07'49.2"</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3°50'45.7"</t>
+          <t>53°07'48.9"</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>237°01'03.4"</t>
+          <t>233°10'18.8"</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>56°58'33.8"</t>
+          <t>53°07'48.3"</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>57°01'04.1"</t>
+          <t>53°10'17.7"</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>56°58'33.8"</t>
+          <t>53°07'48.3"</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1097,29 +1097,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68°14'23.9"</t>
+          <t>57°01'03.5"</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>68°11'54.6"</t>
+          <t>56°58'33.3"</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11°13'20.8"</t>
+          <t>3°50'45.0"</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1137,29 +1137,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>248°14'25.3"</t>
+          <t>237°01'03.1"</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>68°11'54.6"</t>
+          <t>56°58'33.3"</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11°13'20.8"</t>
+          <t>3°50'45.0"</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>327°01'05.4"</t>
+          <t>323°10'18.4"</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>56°58'34.8"</t>
+          <t>53°07'48.9"</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>147°01'04.2"</t>
+          <t>143°10'19.3"</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>56°58'34.8"</t>
+          <t>53°07'48.9"</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1257,29 +1257,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>158°14'25.6"</t>
+          <t>147°01'04.4"</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>68°11'55.7"</t>
+          <t>56°58'34.8"</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11°13'20.8"</t>
+          <t>3°50'45.9"</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1297,29 +1297,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>338°14'25.8"</t>
+          <t>327°01'05.2"</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>68°11'55.7"</t>
+          <t>56°58'34.8"</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>11°13'20.8"</t>
+          <t>3°50'45.9"</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>248°14'25.8"</t>
+          <t>237°01'04.2"</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>68°11'55.9"</t>
+          <t>56°58'33.6"</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1359,7 +1359,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1377,17 +1377,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>68°14'26.1"</t>
+          <t>57°01'03.0"</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>68°11'55.9"</t>
+          <t>56°58'33.6"</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,29 +1417,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>62°29'21.7"</t>
+          <t>68°14'27.3"</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>62°26'50.9"</t>
+          <t>68°11'57.4"</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>354°14'55.0"</t>
+          <t>11°13'23.8"</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1457,29 +1457,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>242°29'20.1"</t>
+          <t>248°14'27.5"</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>62°26'50.9"</t>
+          <t>68°11'57.4"</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>354°14'55.0"</t>
+          <t>11°13'23.8"</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1497,17 +1497,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>338°14'24.7"</t>
+          <t>327°01'05.9"</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>68°11'54.6"</t>
+          <t>56°58'35.1"</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>158°14'24.4"</t>
+          <t>147°01'04.3"</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>68°11'54.6"</t>
+          <t>56°58'35.1"</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1577,29 +1577,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>152°29'20.6"</t>
+          <t>158°14'25.0"</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>62°26'49.5"</t>
+          <t>68°11'55.5"</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>354°14'55.0"</t>
+          <t>11°13'20.4"</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1617,29 +1617,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>332°29'18.5"</t>
+          <t>338°14'26.0"</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>62°26'49.5"</t>
+          <t>68°11'55.5"</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>354°14'55.0"</t>
+          <t>11°13'20.4"</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>242°29'19.7"</t>
+          <t>248°14'24.9"</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>62°26'49.8"</t>
+          <t>68°11'55.0"</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>62°29'19.9"</t>
+          <t>68°14'25.1"</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>62°26'49.8"</t>
+          <t>68°11'55.0"</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1719,7 +1719,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1737,29 +1737,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>61°25'52.4"</t>
+          <t>62°29'22.7"</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>61°23'22.3"</t>
+          <t>62°26'52.8"</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>358°56'32.5"</t>
+          <t>354°14'57.8"</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1777,29 +1777,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>241°25'52.1"</t>
+          <t>242°29'23.0"</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>61°23'22.3"</t>
+          <t>62°26'52.8"</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>358°56'32.5"</t>
+          <t>354°14'57.8"</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>332°29'18.9"</t>
+          <t>338°14'23.9"</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>62°26'50.1"</t>
+          <t>68°11'55.0"</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>152°29'21.2"</t>
+          <t>158°14'26.2"</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>62°26'50.1"</t>
+          <t>68°11'55.0"</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>151°25'53.5"</t>
+          <t>152°29'21.6"</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1907,19 +1907,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>61°23'22.5"</t>
+          <t>62°26'50.7"</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>358°56'32.5"</t>
+          <t>354°14'55.6"</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>331°25'51.5"</t>
+          <t>332°29'19.7"</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1947,19 +1947,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>61°23'22.5"</t>
+          <t>62°26'50.7"</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>358°56'32.5"</t>
+          <t>354°14'55.6"</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>241°25'52.0"</t>
+          <t>242°29'18.5"</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>61°23'21.8"</t>
+          <t>62°26'49.4"</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1999,7 +1999,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>61°25'51.6"</t>
+          <t>62°29'20.2"</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>61°23'21.8"</t>
+          <t>62°26'49.4"</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2057,29 +2057,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>66°17'30.5"</t>
+          <t>61°25'51.3"</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>66°15'01.3"</t>
+          <t>61°23'22.3"</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4°51'39.5"</t>
+          <t>358°56'32.9"</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2097,29 +2097,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>246°17'32.1"</t>
+          <t>241°25'53.3"</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>66°15'01.3"</t>
+          <t>61°23'22.3"</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4°51'39.5"</t>
+          <t>358°56'32.9"</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>331°25'50.8"</t>
+          <t>332°29'19.6"</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>61°23'21.7"</t>
+          <t>62°26'49.3"</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>151°25'52.6"</t>
+          <t>152°29'19.0"</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>61°23'21.7"</t>
+          <t>62°26'49.3"</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2199,7 +2199,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2217,29 +2217,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>156°17'30.5"</t>
+          <t>151°25'50.4"</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>66°15'01.1"</t>
+          <t>61°23'20.0"</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4°51'39.5"</t>
+          <t>358°56'30.7"</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2257,29 +2257,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>336°17'31.8"</t>
+          <t>331°25'49.6"</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>66°15'01.1"</t>
+          <t>61°23'20.0"</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4°51'39.5"</t>
+          <t>358°56'30.7"</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>246°17'32.5"</t>
+          <t>241°25'52.6"</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>66°15'02.0"</t>
+          <t>61°23'23.3"</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2319,7 +2319,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2337,17 +2337,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>66°17'31.6"</t>
+          <t>61°25'54.0"</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>66°15'02.0"</t>
+          <t>61°23'23.3"</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2359,7 +2359,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2377,29 +2377,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>70°14'35.7"</t>
+          <t>66°17'30.5"</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>70°12'04.3"</t>
+          <t>66°15'01.4"</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3°57'02.2"</t>
+          <t>4°51'38.1"</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2417,29 +2417,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>250°14'32.8"</t>
+          <t>246°17'32.2"</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>70°12'04.3"</t>
+          <t>66°15'01.4"</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3°57'02.2"</t>
+          <t>4°51'38.1"</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2457,17 +2457,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>336°17'30.8"</t>
+          <t>331°25'52.4"</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>66°15'01.5"</t>
+          <t>61°23'22.3"</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2479,7 +2479,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2497,17 +2497,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>156°17'32.1"</t>
+          <t>151°25'52.3"</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>66°15'01.5"</t>
+          <t>61°23'22.3"</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2537,29 +2537,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>160°14'32.9"</t>
+          <t>156°17'29.2"</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>70°12'03.7"</t>
+          <t>66°15'01.1"</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3°57'02.2"</t>
+          <t>4°51'38.8"</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2577,29 +2577,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>340°14'34.5"</t>
+          <t>336°17'33.0"</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>70°12'03.7"</t>
+          <t>66°15'01.1"</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3°57'02.2"</t>
+          <t>4°51'38.8"</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>250°14'33.8"</t>
+          <t>246°17'30.8"</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>70°12'04.0"</t>
+          <t>66°15'02.1"</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2657,17 +2657,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>70°14'34.3"</t>
+          <t>66°17'33.4"</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>70°12'04.0"</t>
+          <t>66°15'02.1"</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2679,7 +2679,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2697,29 +2697,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>68°14'25.0"</t>
+          <t>70°14'35.6"</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>68°11'54.9"</t>
+          <t>70°12'05.2"</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>357°59'50.9"</t>
+          <t>3°57'03.1"</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2737,29 +2737,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>248°14'24.9"</t>
+          <t>250°14'34.7"</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>68°11'54.9"</t>
+          <t>70°12'05.2"</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>357°59'50.9"</t>
+          <t>3°57'03.1"</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>340°14'33.2"</t>
+          <t>336°17'31.6"</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>70°12'02.8"</t>
+          <t>66°15'01.7"</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2817,17 +2817,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>160°14'32.3"</t>
+          <t>156°17'31.8"</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>70°12'02.8"</t>
+          <t>66°15'01.7"</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2857,29 +2857,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>158°14'24.0"</t>
+          <t>160°14'35.8"</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>68°11'53.7"</t>
+          <t>70°12'04.8"</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>357°59'50.9"</t>
+          <t>3°57'03.1"</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2897,29 +2897,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>338°14'23.3"</t>
+          <t>340°14'33.8"</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>68°11'53.7"</t>
+          <t>70°12'04.8"</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>357°59'50.9"</t>
+          <t>3°57'03.1"</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2937,17 +2937,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>248°14'24.5"</t>
+          <t>250°14'33.3"</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>68°11'54.1"</t>
+          <t>70°12'03.4"</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2959,7 +2959,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2977,17 +2977,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>68°14'23.6"</t>
+          <t>70°14'33.4"</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>68°11'54.1"</t>
+          <t>70°12'03.4"</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3017,29 +3017,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>72°17'48.1"</t>
+          <t>68°14'24.8"</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>72°15'18.3"</t>
+          <t>68°11'54.2"</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4°03'24.3"</t>
+          <t>357°59'50.8"</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3057,29 +3057,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>252°17'48.5"</t>
+          <t>248°14'23.5"</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>72°15'18.3"</t>
+          <t>68°11'54.2"</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4°03'24.3"</t>
+          <t>357°59'50.8"</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3097,17 +3097,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>338°14'25.1"</t>
+          <t>340°14'34.9"</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>68°11'55.2"</t>
+          <t>70°12'04.1"</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>158°14'25.2"</t>
+          <t>160°14'33.3"</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>68°11'55.2"</t>
+          <t>70°12'04.1"</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3159,7 +3159,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3177,29 +3177,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>162°17'50.4"</t>
+          <t>158°14'26.6"</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>72°15'19.4"</t>
+          <t>68°11'57.5"</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4°03'24.3"</t>
+          <t>357°59'53.4"</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3217,29 +3217,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>342°17'48.4"</t>
+          <t>338°14'28.4"</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>72°15'19.4"</t>
+          <t>68°11'57.5"</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4°03'24.3"</t>
+          <t>357°59'53.4"</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3257,17 +3257,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>252°17'48.5"</t>
+          <t>248°14'25.9"</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>72°15'18.5"</t>
+          <t>68°11'55.7"</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3279,7 +3279,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>72°17'48.5"</t>
+          <t>68°14'25.6"</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>72°15'18.5"</t>
+          <t>68°11'55.7"</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K9</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3337,29 +3337,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>63°28'35.1"</t>
+          <t>72°17'50.6"</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>63°26'05.1"</t>
+          <t>72°15'21.2"</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>351°10'46.6"</t>
+          <t>4°03'25.4"</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K9</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3377,29 +3377,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>243°28'35.2"</t>
+          <t>252°17'51.7"</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>63°26'05.1"</t>
+          <t>72°15'21.2"</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>351°10'46.6"</t>
+          <t>4°03'25.4"</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>342°17'49.7"</t>
+          <t>338°14'23.5"</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>72°15'19.6"</t>
+          <t>68°11'55.0"</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>K8</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>162°17'49.6"</t>
+          <t>158°14'26.5"</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>72°15'19.6"</t>
+          <t>68°11'55.0"</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3479,7 +3479,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K9</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3497,29 +3497,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>153°28'37.2"</t>
+          <t>162°17'49.3"</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>63°26'06.3"</t>
+          <t>72°15'18.9"</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>351°10'46.6"</t>
+          <t>4°03'23.9"</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>K8</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3527,32 +3527,672 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>342°17'48.4"</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>72°15'18.9"</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>4°03'23.9"</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>252°17'50.7"</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>72°15'20.3"</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>72°17'49.9"</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>72°15'20.3"</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
           <t>G</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>63°28'37.2"</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>63°26'09.3"</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>351°10'49.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>333°28'35.3"</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>63°26'06.3"</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>351°10'46.6"</t>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>243°28'41.3"</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>63°26'09.3"</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>351°10'49.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>342°17'48.7"</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>72°15'18.9"</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>162°17'49.1"</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>72°15'18.9"</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>153°28'34.3"</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>63°26'04.4"</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>351°10'45.5"</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>333°28'34.4"</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>63°26'04.4"</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>351°10'45.5"</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>243°28'35.5"</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>63°26'06.2"</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>63°28'37.0"</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>63°26'06.2"</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>63°28'37.6"</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>63°26'07.9"</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0°00'01.7"</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>243°28'38.3"</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>63°26'07.9"</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0°00'01.7"</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>333°28'36.1"</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>63°26'05.8"</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>153°28'35.6"</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>63°26'05.8"</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>153°28'35.1"</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-2.11</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>63°26'06.1"</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0°00'00.3"</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>333°28'37.2"</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-2.11</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>63°26'06.1"</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0°00'00.3"</t>
         </is>
       </c>
     </row>
@@ -3575,7 +4215,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3634,22 +4274,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>250</v>
+        <v>249.9994344026943</v>
       </c>
       <c r="D2" t="n">
-        <v>250</v>
+        <v>249.9991386552885</v>
       </c>
       <c r="E2" t="n">
-        <v>250</v>
+        <v>250.0011299064051</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.991251116550075</v>
       </c>
       <c r="G2" t="n">
-        <v>250</v>
+        <v>249.9999009881293</v>
       </c>
       <c r="H2" t="n">
-        <v>250</v>
+        <v>250.000183879047</v>
       </c>
     </row>
     <row r="3">
@@ -3664,22 +4304,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>250</v>
+        <v>250.0007268623388</v>
       </c>
       <c r="D3" t="n">
-        <v>250</v>
+        <v>250.0002074079613</v>
       </c>
       <c r="E3" t="n">
-        <v>250</v>
+        <v>249.99875264807</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.974214268813057</v>
       </c>
       <c r="G3" t="n">
-        <v>250</v>
+        <v>249.9998956394567</v>
       </c>
       <c r="H3" t="n">
-        <v>250</v>
+        <v>250.000183879047</v>
       </c>
     </row>
     <row r="4">
@@ -3694,22 +4334,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>250</v>
+        <v>249.999743187287</v>
       </c>
       <c r="D4" t="n">
-        <v>250</v>
+        <v>250.0005482843943</v>
       </c>
       <c r="E4" t="n">
-        <v>250</v>
+        <v>250.0004443582251</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.8050971072748325</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>250.0002452766355</v>
       </c>
       <c r="H4" t="n">
-        <v>250</v>
+        <v>250.000183879047</v>
       </c>
     </row>
     <row r="5">
@@ -3724,22 +4364,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>250</v>
+        <v>250.0001670063624</v>
       </c>
       <c r="D5" t="n">
-        <v>250</v>
+        <v>250.0012510765717</v>
       </c>
       <c r="E5" t="n">
-        <v>250</v>
+        <v>250.000662752966</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.084070209316224</v>
       </c>
       <c r="G5" t="n">
-        <v>250</v>
+        <v>250.0006936119667</v>
       </c>
       <c r="H5" t="n">
-        <v>250</v>
+        <v>250.000183879047</v>
       </c>
     </row>
     <row r="6">
@@ -3754,22 +4394,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5361636059582</v>
       </c>
       <c r="D6" t="n">
-        <v>238.5372088375313</v>
+        <v>238.536811080139</v>
       </c>
       <c r="E6" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5386898564733</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2.526250515103357</v>
       </c>
       <c r="G6" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5372215141902</v>
       </c>
       <c r="H6" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5372246790685</v>
       </c>
     </row>
     <row r="7">
@@ -3784,22 +4424,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5368953977976</v>
       </c>
       <c r="D7" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5357918199799</v>
       </c>
       <c r="E7" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5372515148942</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.459694914274223</v>
       </c>
       <c r="G7" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5366462442239</v>
       </c>
       <c r="H7" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5372246790685</v>
       </c>
     </row>
     <row r="8">
@@ -3814,22 +4454,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5375133670806</v>
       </c>
       <c r="D8" t="n">
-        <v>238.5372088375313</v>
+        <v>238.536488662365</v>
       </c>
       <c r="E8" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5358643543692</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.649012711482101</v>
       </c>
       <c r="G8" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5366221279382</v>
       </c>
       <c r="H8" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5372246790685</v>
       </c>
     </row>
     <row r="9">
@@ -3844,22 +4484,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>238.5372088375313</v>
+        <v>238.538242066319</v>
       </c>
       <c r="D9" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5391324644229</v>
       </c>
       <c r="E9" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5378519590232</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.280505399705589</v>
       </c>
       <c r="G9" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5384088299217</v>
       </c>
       <c r="H9" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5372246790685</v>
       </c>
     </row>
     <row r="10">
@@ -3874,22 +4514,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2580357083636</v>
       </c>
       <c r="D10" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2606712090646</v>
       </c>
       <c r="E10" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2583345191028</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2.635500700989724</v>
       </c>
       <c r="G10" t="n">
-        <v>269.2582403567252</v>
+        <v>269.259013812177</v>
       </c>
       <c r="H10" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2583940326871</v>
       </c>
     </row>
     <row r="11">
@@ -3904,22 +4544,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2588768496997</v>
       </c>
       <c r="D11" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2596249919281</v>
       </c>
       <c r="E11" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2579569064043</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.668085523874652</v>
       </c>
       <c r="G11" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2588195826774</v>
       </c>
       <c r="H11" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2583940326871</v>
       </c>
     </row>
     <row r="12">
@@ -3934,22 +4574,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>269.2582403567252</v>
+        <v>269.256420231476</v>
       </c>
       <c r="D12" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2587119215781</v>
       </c>
       <c r="E12" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2561473988183</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2.564522759826104</v>
       </c>
       <c r="G12" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2570931839575</v>
       </c>
       <c r="H12" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2583940326871</v>
       </c>
     </row>
     <row r="13">
@@ -3964,22 +4604,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2573547414996</v>
       </c>
       <c r="D13" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2596516028237</v>
       </c>
       <c r="E13" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2589423114856</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2.296861324111887</v>
       </c>
       <c r="G13" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2586495519363</v>
       </c>
       <c r="H13" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2583940326871</v>
       </c>
     </row>
     <row r="14">
@@ -3994,22 +4634,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>259.422435421457</v>
+        <v>259.4226117779279</v>
       </c>
       <c r="D14" t="n">
-        <v>259.422435421457</v>
+        <v>259.4206996485031</v>
       </c>
       <c r="E14" t="n">
-        <v>259.422435421457</v>
+        <v>259.4208570671505</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.912129424795239</v>
       </c>
       <c r="G14" t="n">
-        <v>259.422435421457</v>
+        <v>259.4213894978605</v>
       </c>
       <c r="H14" t="n">
-        <v>259.422435421457</v>
+        <v>259.4222028208943</v>
       </c>
     </row>
     <row r="15">
@@ -4024,22 +4664,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>259.422435421457</v>
+        <v>259.4208998025648</v>
       </c>
       <c r="D15" t="n">
-        <v>259.422435421457</v>
+        <v>259.4244245194303</v>
       </c>
       <c r="E15" t="n">
-        <v>259.422435421457</v>
+        <v>259.422144616495</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3.524716865513255</v>
       </c>
       <c r="G15" t="n">
-        <v>259.422435421457</v>
+        <v>259.4224896461633</v>
       </c>
       <c r="H15" t="n">
-        <v>259.422435421457</v>
+        <v>259.4222028208943</v>
       </c>
     </row>
     <row r="16">
@@ -4054,22 +4694,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>259.422435421457</v>
+        <v>259.4200570219994</v>
       </c>
       <c r="D16" t="n">
-        <v>259.422435421457</v>
+        <v>259.4226156734802</v>
       </c>
       <c r="E16" t="n">
-        <v>259.422435421457</v>
+        <v>259.4238741168383</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3.817094838950652</v>
       </c>
       <c r="G16" t="n">
-        <v>259.422435421457</v>
+        <v>259.4221822707726</v>
       </c>
       <c r="H16" t="n">
-        <v>259.422435421457</v>
+        <v>259.4222028208943</v>
       </c>
     </row>
     <row r="17">
@@ -4084,22 +4724,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>259.422435421457</v>
+        <v>259.4234557577832</v>
       </c>
       <c r="D17" t="n">
-        <v>259.422435421457</v>
+        <v>259.4229701886132</v>
       </c>
       <c r="E17" t="n">
-        <v>259.422435421457</v>
+        <v>259.4218236599463</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.632097836932189</v>
       </c>
       <c r="G17" t="n">
-        <v>259.422435421457</v>
+        <v>259.422749868781</v>
       </c>
       <c r="H17" t="n">
-        <v>259.422435421457</v>
+        <v>259.4222028208943</v>
       </c>
     </row>
     <row r="18">
@@ -4114,22 +4754,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>250.5992817228334</v>
+        <v>250.6006838238786</v>
       </c>
       <c r="D18" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5994530295615</v>
       </c>
       <c r="E18" t="n">
-        <v>250.5992817228334</v>
+        <v>250.6009181203943</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.465090832766691</v>
       </c>
       <c r="G18" t="n">
-        <v>250.5992817228334</v>
+        <v>250.6003516579448</v>
       </c>
       <c r="H18" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5998753079505</v>
       </c>
     </row>
     <row r="19">
@@ -4144,22 +4784,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5998914451755</v>
       </c>
       <c r="D19" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5996636995412</v>
       </c>
       <c r="E19" t="n">
-        <v>250.5992817228334</v>
+        <v>250.6002755718566</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.6118723154031613</v>
       </c>
       <c r="G19" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5999435721911</v>
       </c>
       <c r="H19" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5998753079505</v>
       </c>
     </row>
     <row r="20">
@@ -4174,22 +4814,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5982383166882</v>
       </c>
       <c r="D20" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5982190269745</v>
       </c>
       <c r="E20" t="n">
-        <v>250.5992817228334</v>
+        <v>250.6006322646659</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.413237691342829</v>
       </c>
       <c r="G20" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5990298694429</v>
       </c>
       <c r="H20" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5998753079505</v>
       </c>
     </row>
     <row r="21">
@@ -4204,22 +4844,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>250.5992817228334</v>
+        <v>250.599780471831</v>
       </c>
       <c r="D21" t="n">
-        <v>250.5992817228334</v>
+        <v>250.6006161767641</v>
       </c>
       <c r="E21" t="n">
-        <v>250.5992817228334</v>
+        <v>250.6001317480748</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.8357049331095823</v>
       </c>
       <c r="G21" t="n">
-        <v>250.5992817228334</v>
+        <v>250.6001761322233</v>
       </c>
       <c r="H21" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5998753079505</v>
       </c>
     </row>
     <row r="22">
@@ -4234,22 +4874,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1303781616347</v>
       </c>
       <c r="D22" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1298207007438</v>
       </c>
       <c r="E22" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1278221987736</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2.555962861151784</v>
       </c>
       <c r="G22" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1293403537174</v>
       </c>
       <c r="H22" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1293452679554</v>
       </c>
     </row>
     <row r="23">
@@ -4264,22 +4904,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1295822725099</v>
       </c>
       <c r="D23" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1285363487251</v>
       </c>
       <c r="E23" t="n">
-        <v>273.1300056749533</v>
+        <v>273.128449524035</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1.132748474901746</v>
       </c>
       <c r="G23" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1288560484234</v>
       </c>
       <c r="H23" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1293452679554</v>
       </c>
     </row>
     <row r="24">
@@ -4294,22 +4934,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1301572049059</v>
       </c>
       <c r="D24" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1290515125729</v>
       </c>
       <c r="E24" t="n">
-        <v>273.1300056749533</v>
+        <v>273.129842540051</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.105692332998842</v>
       </c>
       <c r="G24" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1296837525099</v>
       </c>
       <c r="H24" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1293452679554</v>
       </c>
     </row>
     <row r="25">
@@ -4324,22 +4964,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1300228477116</v>
       </c>
       <c r="D25" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1299213302732</v>
       </c>
       <c r="E25" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1285585735271</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.46427418451367</v>
       </c>
       <c r="G25" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1295009171707</v>
       </c>
       <c r="H25" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1293452679554</v>
       </c>
     </row>
     <row r="26">
@@ -4354,22 +4994,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7060827103276</v>
       </c>
       <c r="D26" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7066406783247</v>
       </c>
       <c r="E26" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7059606866754</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.679991649292333</v>
       </c>
       <c r="G26" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7062280251092</v>
       </c>
       <c r="H26" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7063842434742</v>
       </c>
     </row>
     <row r="27">
@@ -4384,22 +5024,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7061908109842</v>
       </c>
       <c r="D27" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7058194903726</v>
       </c>
       <c r="E27" t="n">
-        <v>265.7066051117284</v>
+        <v>265.705464886374</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.7259246101511962</v>
       </c>
       <c r="G27" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7058250625769</v>
       </c>
       <c r="H27" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7063842434742</v>
       </c>
     </row>
     <row r="28">
@@ -4414,22 +5054,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7083613107006</v>
       </c>
       <c r="D28" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7033318850615</v>
       </c>
       <c r="E28" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7051685448115</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>5.029425639065721</v>
       </c>
       <c r="G28" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7056205801912</v>
       </c>
       <c r="H28" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7063842434742</v>
       </c>
     </row>
     <row r="29">
@@ -4444,22 +5084,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7087440897724</v>
       </c>
       <c r="D29" t="n">
-        <v>265.7066051117284</v>
+        <v>265.706883052034</v>
       </c>
       <c r="E29" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7079627762524</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1.861037738365212</v>
       </c>
       <c r="G29" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7078633060196</v>
       </c>
       <c r="H29" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7063842434742</v>
       </c>
     </row>
     <row r="30">
@@ -4474,22 +5114,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2604292826456</v>
       </c>
       <c r="D30" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2581152679006</v>
       </c>
       <c r="E30" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2599118164789</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2.314014745024906</v>
       </c>
       <c r="G30" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2594854556751</v>
       </c>
       <c r="H30" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2588004827543</v>
       </c>
     </row>
     <row r="31">
@@ -4504,22 +5144,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2559540489731</v>
       </c>
       <c r="D31" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2589950159403</v>
       </c>
       <c r="E31" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2588332018733</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>3.040966967262193</v>
       </c>
       <c r="G31" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2579274222622</v>
       </c>
       <c r="H31" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2588004827543</v>
       </c>
     </row>
     <row r="32">
@@ -4534,22 +5174,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2574006972206</v>
       </c>
       <c r="D32" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2600763322647</v>
       </c>
       <c r="E32" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2594743050744</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2.675635044056435</v>
       </c>
       <c r="G32" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2589837781866</v>
       </c>
       <c r="H32" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2588004827543</v>
       </c>
     </row>
     <row r="33">
@@ -4564,22 +5204,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2585600412746</v>
       </c>
       <c r="D33" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2581417758013</v>
       </c>
       <c r="E33" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2597140076035</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.572231802128954</v>
       </c>
       <c r="G33" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2588052748931</v>
       </c>
       <c r="H33" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2588004827543</v>
       </c>
     </row>
     <row r="34">
@@ -4594,22 +5234,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4864180580219</v>
       </c>
       <c r="D34" t="n">
-        <v>262.4880949681337</v>
+        <v>262.48816421222</v>
       </c>
       <c r="E34" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4882803424425</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.862284420610649</v>
       </c>
       <c r="G34" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4876208708948</v>
       </c>
       <c r="H34" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4877771880526</v>
       </c>
     </row>
     <row r="35">
@@ -4624,22 +5264,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4887295909769</v>
       </c>
       <c r="D35" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4879757810253</v>
       </c>
       <c r="E35" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4876339263756</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.095664601336921</v>
       </c>
       <c r="G35" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4881130994593</v>
       </c>
       <c r="H35" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4877771880526</v>
       </c>
     </row>
     <row r="36">
@@ -4654,22 +5294,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4867685785847</v>
       </c>
       <c r="D36" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4882173150687</v>
       </c>
       <c r="E36" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4885189364234</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1.750357838716354</v>
       </c>
       <c r="G36" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4878349433589</v>
       </c>
       <c r="H36" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4877771880526</v>
       </c>
     </row>
     <row r="37">
@@ -4684,22 +5324,22 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4861870116756</v>
       </c>
       <c r="D37" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4888648860446</v>
       </c>
       <c r="E37" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4875676177732</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2.677874368941957</v>
       </c>
       <c r="G37" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4875398384978</v>
       </c>
       <c r="H37" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4877771880526</v>
       </c>
     </row>
     <row r="38">
@@ -4714,22 +5354,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>223.606797749979</v>
+        <v>223.6062562874748</v>
       </c>
       <c r="D38" t="n">
-        <v>223.606797749979</v>
+        <v>223.6072594638994</v>
       </c>
       <c r="E38" t="n">
-        <v>223.606797749979</v>
+        <v>223.6057151358536</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1.544328045724797</v>
       </c>
       <c r="G38" t="n">
-        <v>223.6067977499789</v>
+        <v>223.6064102957426</v>
       </c>
       <c r="H38" t="n">
-        <v>223.6067977499789</v>
+        <v>223.6066970318542</v>
       </c>
     </row>
     <row r="39">
@@ -4744,22 +5384,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>223.606797749979</v>
+        <v>223.6059547757879</v>
       </c>
       <c r="D39" t="n">
-        <v>223.606797749979</v>
+        <v>223.6058113368083</v>
       </c>
       <c r="E39" t="n">
-        <v>223.606797749979</v>
+        <v>223.6087077843794</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2.896447571089311</v>
       </c>
       <c r="G39" t="n">
-        <v>223.6067977499789</v>
+        <v>223.6068246323252</v>
       </c>
       <c r="H39" t="n">
-        <v>223.6067977499789</v>
+        <v>223.6066970318542</v>
       </c>
     </row>
     <row r="40">
@@ -4774,22 +5414,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>223.606797749979</v>
+        <v>223.6058270144835</v>
       </c>
       <c r="D40" t="n">
-        <v>223.606797749979</v>
+        <v>223.6072618314378</v>
       </c>
       <c r="E40" t="n">
-        <v>223.606797749979</v>
+        <v>223.606452882359</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1.434816954315465</v>
       </c>
       <c r="G40" t="n">
-        <v>223.6067977499789</v>
+        <v>223.6065139094268</v>
       </c>
       <c r="H40" t="n">
-        <v>223.6067977499789</v>
+        <v>223.6066970318542</v>
       </c>
     </row>
     <row r="41">
@@ -4804,22 +5444,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>223.606797749979</v>
+        <v>223.6085586890833</v>
       </c>
       <c r="D41" t="n">
-        <v>223.606797749979</v>
+        <v>223.6064436939352</v>
       </c>
       <c r="E41" t="n">
-        <v>223.606797749979</v>
+        <v>223.6061154867477</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2.443202335683736</v>
       </c>
       <c r="G41" t="n">
-        <v>223.6067977499789</v>
+        <v>223.6070392899221</v>
       </c>
       <c r="H41" t="n">
-        <v>223.6067977499789</v>
+        <v>223.6066970318542</v>
       </c>
     </row>
   </sheetData>
@@ -4833,17 +5473,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4912,20 +5552,24 @@
           <t>→edge_B_K1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>233°07'50.3"</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>53°07'48.4"</t>
+          <t>53°07'50.3"</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>250</v>
+        <v>250.000183879047</v>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>149.9982560268532</v>
       </c>
       <c r="F3" t="n">
-        <v>200</v>
+        <v>200.0015378152376</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -4938,7 +5582,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>183°50'45.7"</t>
+          <t>183°50'45.5"</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -4946,10 +5590,10 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>10150</v>
+        <v>10149.99825602685</v>
       </c>
       <c r="H4" t="n">
-        <v>5200</v>
+        <v>5200.001537815237</v>
       </c>
     </row>
     <row r="5">
@@ -4960,22 +5604,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>183°50'45.7"</t>
+          <t>183°50'45.5"</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56°58'34.1"</t>
+          <t>56°58'35.8"</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>238.5372088375313</v>
+        <v>238.5372246790685</v>
       </c>
       <c r="E5" t="n">
-        <v>130.0000000000003</v>
+        <v>129.9983751601969</v>
       </c>
       <c r="F5" t="n">
-        <v>199.9999999999998</v>
+        <v>200.0010750303636</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -4988,7 +5632,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>191°13'20.8"</t>
+          <t>191°13'22.1"</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -4996,10 +5640,10 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>10280</v>
+        <v>10279.99663118705</v>
       </c>
       <c r="H6" t="n">
-        <v>5400</v>
+        <v>5400.002612845601</v>
       </c>
     </row>
     <row r="7">
@@ -5010,22 +5654,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>191°13'20.8"</t>
+          <t>191°13'22.1"</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>68°11'54.9"</t>
+          <t>68°11'57.9"</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2583940326871</v>
       </c>
       <c r="E7" t="n">
-        <v>100.0000000000007</v>
+        <v>99.99648708430313</v>
       </c>
       <c r="F7" t="n">
-        <v>249.9999999999997</v>
+        <v>250.0015706507873</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -5038,7 +5682,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>174°14'55.0"</t>
+          <t>174°14'56.7"</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -5046,10 +5690,10 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>10380</v>
+        <v>10379.99311827135</v>
       </c>
       <c r="H8" t="n">
-        <v>5650</v>
+        <v>5650.004183496389</v>
       </c>
     </row>
     <row r="9">
@@ -5060,22 +5704,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>174°14'55.0"</t>
+          <t>174°14'56.7"</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>62°26'49.9"</t>
+          <t>62°26'54.6"</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>259.422435421457</v>
+        <v>259.4222028208943</v>
       </c>
       <c r="E9" t="n">
-        <v>120.0000000000005</v>
+        <v>119.9946304345739</v>
       </c>
       <c r="F9" t="n">
-        <v>229.9999999999997</v>
+        <v>230.0025390801485</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -5088,7 +5732,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>178°56'32.5"</t>
+          <t>178°56'31.8"</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -5096,10 +5740,10 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>10500</v>
+        <v>10499.98774870593</v>
       </c>
       <c r="H10" t="n">
-        <v>5880</v>
+        <v>5880.006722576537</v>
       </c>
     </row>
     <row r="11">
@@ -5110,22 +5754,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>178°56'32.5"</t>
+          <t>178°56'31.8"</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>61°23'22.3"</t>
+          <t>61°23'26.4"</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>250.5992817228334</v>
+        <v>250.5998753079505</v>
       </c>
       <c r="E11" t="n">
-        <v>120.0000000000004</v>
+        <v>119.9959456258278</v>
       </c>
       <c r="F11" t="n">
-        <v>219.9999999999998</v>
+        <v>220.0028875667857</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -5138,7 +5782,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>184°51'39.5"</t>
+          <t>184°51'38.4"</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -5146,10 +5790,10 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>10620</v>
+        <v>10619.98369433176</v>
       </c>
       <c r="H12" t="n">
-        <v>6100</v>
+        <v>6100.009610143323</v>
       </c>
     </row>
     <row r="13">
@@ -5160,22 +5804,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>184°51'39.5"</t>
+          <t>184°51'38.4"</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>66°15'01.8"</t>
+          <t>66°15'04.8"</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>273.1300056749533</v>
+        <v>273.1293452679553</v>
       </c>
       <c r="E13" t="n">
-        <v>110.0000000000005</v>
+        <v>109.996067416877</v>
       </c>
       <c r="F13" t="n">
-        <v>249.9999999999998</v>
+        <v>250.0010087966122</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -5188,7 +5832,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>183°57'02.2"</t>
+          <t>183°57'03.1"</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -5196,10 +5840,10 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>10730</v>
+        <v>10729.97976174863</v>
       </c>
       <c r="H14" t="n">
-        <v>6350</v>
+        <v>6350.010618939935</v>
       </c>
     </row>
     <row r="15">
@@ -5210,22 +5854,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>183°57'02.2"</t>
+          <t>183°57'03.1"</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>70°12'04.0"</t>
+          <t>70°12'07.9"</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>265.7066051117284</v>
+        <v>265.7063842434742</v>
       </c>
       <c r="E15" t="n">
-        <v>90.00000000000077</v>
+        <v>89.99521451598818</v>
       </c>
       <c r="F15" t="n">
-        <v>249.9999999999997</v>
+        <v>250.0014879794959</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -5238,7 +5882,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>177°59'50.9"</t>
+          <t>177°59'52.1"</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -5246,10 +5890,10 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>10820</v>
+        <v>10819.97497626462</v>
       </c>
       <c r="H16" t="n">
-        <v>6600</v>
+        <v>6600.012106919431</v>
       </c>
     </row>
     <row r="17">
@@ -5260,22 +5904,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>177°59'50.9"</t>
+          <t>177°59'52.1"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>68°11'54.9"</t>
+          <t>68°12'00.1"</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>269.2582403567252</v>
+        <v>269.2588004827543</v>
       </c>
       <c r="E17" t="n">
-        <v>100.0000000000009</v>
+        <v>99.99397782401354</v>
       </c>
       <c r="F17" t="n">
-        <v>249.9999999999996</v>
+        <v>250.0030120545398</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -5288,7 +5932,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>184°03'24.3"</t>
+          <t>184°03'24.6"</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -5296,10 +5940,10 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>10920</v>
+        <v>10919.96895408863</v>
       </c>
       <c r="H18" t="n">
-        <v>6850</v>
+        <v>6850.015118973971</v>
       </c>
     </row>
     <row r="19">
@@ -5310,22 +5954,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>184°03'24.3"</t>
+          <t>184°03'24.6"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>72°15'19.2"</t>
+          <t>72°15'24.7"</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>262.4880949681337</v>
+        <v>262.4877771880527</v>
       </c>
       <c r="E19" t="n">
-        <v>80.00000000000117</v>
+        <v>79.99319958693836</v>
       </c>
       <c r="F19" t="n">
-        <v>249.9999999999996</v>
+        <v>250.0018423791494</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -5338,7 +5982,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>171°10'46.6"</t>
+          <t>171°10'47.2"</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -5346,10 +5990,10 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>11000</v>
+        <v>10999.96215367557</v>
       </c>
       <c r="H20" t="n">
-        <v>7100</v>
+        <v>7100.016961353121</v>
       </c>
     </row>
     <row r="21">
@@ -5360,22 +6004,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>171°10'46.6"</t>
+          <t>171°10'47.2"</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>63°26'05.8"</t>
+          <t>63°26'12.0"</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>223.6067977499789</v>
+        <v>223.6066970318541</v>
       </c>
       <c r="E21" t="n">
-        <v>100.0000000000009</v>
+        <v>99.99399857207619</v>
       </c>
       <c r="F21" t="n">
-        <v>199.9999999999995</v>
+        <v>200.0028879968063</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -5392,73 +6036,92 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>11100</v>
+        <v>11099.95615224765</v>
       </c>
       <c r="H22" t="n">
-        <v>7299.999999999999</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+        <v>7300.019849349927</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>→edge_G_G2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>180°00'01.0"</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>63°26'12.9"</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>闭合差项</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>值</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>方位角闭合差(")</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-9.160006086972317e-10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>f_x(m)</t>
+          <t>方位角闭合差(")</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>7.133233264808969</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f_y(m)</t>
+          <t>f_x(m)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>-0.04384775235121197</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f_D(m)</t>
+          <t>f_y(m)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.033691978340166e-12</v>
+        <v>0.01984934992651688</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>f_D(m)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.04813130040585367</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>全长(m)</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>2562.006910200066</v>
+      <c r="B30" t="n">
+        <v>2562.006884933738</v>
       </c>
     </row>
   </sheetData>

--- a/output/一级导线观测手簿.xlsx
+++ b/output/一级导线观测手簿.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B (10000.000, 5000.000)</t>
+          <t>B (101.587, 271.625)</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G (11100.000, 7300.000)</t>
+          <t>G (1520.842, 1604.517)</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -697,17 +697,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>180°02'29.3"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>359°59'58.7"</t>
+          <t>359°59'58.8"</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0°02'28.1"</t>
+          <t>179°59'57.6"</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>359°59'58.7"</t>
+          <t>359°59'58.8"</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -777,22 +777,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53°10'20.0"</t>
+          <t>168°21'45.1"</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>53°07'50.4"</t>
+          <t>168°21'44.5"</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>53°07'51.6"</t>
+          <t>168°21'45.7"</t>
         </is>
       </c>
     </row>
@@ -817,22 +817,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>233°10'20.8"</t>
+          <t>348°21'43.9"</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>53°07'50.4"</t>
+          <t>168°21'44.5"</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>53°07'51.6"</t>
+          <t>168°21'45.7"</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>270°02'31.1"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0°00'00.3"</t>
+          <t>359°59'59.6"</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>90°02'29.5"</t>
+          <t>269°59'59.2"</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0°00'00.3"</t>
+          <t>359°59'59.6"</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -937,22 +937,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>143°10'19.8"</t>
+          <t>258°21'48.7"</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>53°07'49.2"</t>
+          <t>348°21'48.5"</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>53°07'48.9"</t>
+          <t>348°21'48.9"</t>
         </is>
       </c>
     </row>
@@ -977,22 +977,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>323°10'18.6"</t>
+          <t>78°21'48.3"</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>53°07'49.2"</t>
+          <t>348°21'48.5"</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>53°07'48.9"</t>
+          <t>348°21'48.9"</t>
         </is>
       </c>
     </row>
@@ -1017,17 +1017,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>233°10'18.8"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>53°07'48.3"</t>
+          <t>0°00'00.3"</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>53°10'17.7"</t>
+          <t>180°00'00.5"</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>53°07'48.3"</t>
+          <t>0°00'00.3"</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>57°01'03.5"</t>
+          <t>165°41'16.8"</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>56°58'33.3"</t>
+          <t>165°41'16.2"</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3°50'45.0"</t>
+          <t>165°41'16.0"</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>237°01'03.1"</t>
+          <t>345°41'15.7"</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>56°58'33.3"</t>
+          <t>165°41'16.2"</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3°50'45.0"</t>
+          <t>165°41'16.0"</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>323°10'18.4"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>53°07'48.9"</t>
+          <t>359°59'59.2"</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>143°10'19.3"</t>
+          <t>269°59'58.5"</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>53°07'48.9"</t>
+          <t>359°59'59.2"</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,22 +1257,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>147°01'04.4"</t>
+          <t>255°41'17.3"</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>56°58'34.8"</t>
+          <t>345°41'17.2"</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3°50'45.9"</t>
+          <t>345°41'17.9"</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>327°01'05.2"</t>
+          <t>75°41'17.1"</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>56°58'34.8"</t>
+          <t>345°41'17.2"</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3°50'45.9"</t>
+          <t>345°41'17.9"</t>
         </is>
       </c>
     </row>
@@ -1337,17 +1337,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>237°01'04.2"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>56°58'33.6"</t>
+          <t>0°00'00.4"</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1377,17 +1377,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>57°01'03.0"</t>
+          <t>180°00'00.8"</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>56°58'33.6"</t>
+          <t>0°00'00.4"</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>68°14'27.3"</t>
+          <t>204°35'17.4"</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>68°11'57.4"</t>
+          <t>24°35'18.2"</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11°13'23.8"</t>
+          <t>24°35'17.8"</t>
         </is>
       </c>
     </row>
@@ -1457,22 +1457,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>248°14'27.5"</t>
+          <t>24°35'18.9"</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>68°11'57.4"</t>
+          <t>24°35'18.2"</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11°13'23.8"</t>
+          <t>24°35'17.8"</t>
         </is>
       </c>
     </row>
@@ -1497,17 +1497,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>327°01'05.9"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>56°58'35.1"</t>
+          <t>359°59'59.4"</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>147°01'04.3"</t>
+          <t>269°59'58.7"</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>56°58'35.1"</t>
+          <t>359°59'59.4"</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>158°14'25.0"</t>
+          <t>294°35'22.3"</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>68°11'55.5"</t>
+          <t>24°35'22.4"</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11°13'20.4"</t>
+          <t>24°35'23.0"</t>
         </is>
       </c>
     </row>
@@ -1617,22 +1617,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>338°14'26.0"</t>
+          <t>114°35'22.5"</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>68°11'55.5"</t>
+          <t>24°35'22.4"</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>11°13'20.4"</t>
+          <t>24°35'23.0"</t>
         </is>
       </c>
     </row>
@@ -1657,17 +1657,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>248°14'24.9"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>68°11'55.0"</t>
+          <t>0°00'00.2"</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>68°14'25.1"</t>
+          <t>180°00'00.3"</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>68°11'55.0"</t>
+          <t>0°00'00.2"</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1737,22 +1737,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>62°29'22.7"</t>
+          <t>136°00'17.6"</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>62°26'52.8"</t>
+          <t>136°00'16.8"</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>354°14'57.8"</t>
+          <t>136°00'16.6"</t>
         </is>
       </c>
     </row>
@@ -1777,22 +1777,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>242°29'23.0"</t>
+          <t>316°00'15.9"</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>62°26'52.8"</t>
+          <t>136°00'16.8"</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>354°14'57.8"</t>
+          <t>136°00'16.6"</t>
         </is>
       </c>
     </row>
@@ -1817,17 +1817,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>338°14'23.9"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>68°11'55.0"</t>
+          <t>359°59'59.9"</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1857,17 +1857,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>158°14'26.2"</t>
+          <t>269°59'59.7"</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>68°11'55.0"</t>
+          <t>359°59'59.9"</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1897,22 +1897,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>152°29'21.6"</t>
+          <t>226°00'12.4"</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>62°26'50.7"</t>
+          <t>316°00'11.4"</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>354°14'55.6"</t>
+          <t>316°00'11.5"</t>
         </is>
       </c>
     </row>
@@ -1937,22 +1937,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>332°29'19.7"</t>
+          <t>46°00'10.3"</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>62°26'50.7"</t>
+          <t>316°00'11.4"</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>354°14'55.6"</t>
+          <t>316°00'11.5"</t>
         </is>
       </c>
     </row>
@@ -1977,17 +1977,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>242°29'18.5"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>62°26'49.4"</t>
+          <t>0°00'00.1"</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62°29'20.2"</t>
+          <t>180°00'00.3"</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>62°26'49.4"</t>
+          <t>0°00'00.1"</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2057,22 +2057,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>61°25'51.3"</t>
+          <t>177°58'47.7"</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>61°23'22.3"</t>
+          <t>177°58'47.6"</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>358°56'32.9"</t>
+          <t>177°58'47.5"</t>
         </is>
       </c>
     </row>
@@ -2097,22 +2097,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>241°25'53.3"</t>
+          <t>357°58'47.5"</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>61°23'22.3"</t>
+          <t>177°58'47.6"</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>358°56'32.9"</t>
+          <t>177°58'47.5"</t>
         </is>
       </c>
     </row>
@@ -2137,17 +2137,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>332°29'19.6"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>62°26'49.3"</t>
+          <t>0°00'01.2"</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>152°29'19.0"</t>
+          <t>270°00'02.3"</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>62°26'49.3"</t>
+          <t>0°00'01.2"</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>151°25'50.4"</t>
+          <t>267°58'49.6"</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>61°23'20.0"</t>
+          <t>357°58'48.6"</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>358°56'30.7"</t>
+          <t>357°58'47.4"</t>
         </is>
       </c>
     </row>
@@ -2257,22 +2257,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>331°25'49.6"</t>
+          <t>87°58'47.6"</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>61°23'20.0"</t>
+          <t>357°58'48.6"</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>358°56'30.7"</t>
+          <t>357°58'47.4"</t>
         </is>
       </c>
     </row>
@@ -2297,17 +2297,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>241°25'52.6"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>61°23'23.3"</t>
+          <t>359°59'59.8"</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2337,17 +2337,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>61°25'54.0"</t>
+          <t>179°59'59.7"</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>61°23'23.3"</t>
+          <t>359°59'59.8"</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2377,22 +2377,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>66°17'30.5"</t>
+          <t>188°23'22.5"</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>66°15'01.4"</t>
+          <t>8°23'23.3"</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4°51'38.1"</t>
+          <t>8°23'23.5"</t>
         </is>
       </c>
     </row>
@@ -2417,22 +2417,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>246°17'32.2"</t>
+          <t>8°23'24.1"</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>66°15'01.4"</t>
+          <t>8°23'23.3"</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4°51'38.1"</t>
+          <t>8°23'23.5"</t>
         </is>
       </c>
     </row>
@@ -2457,17 +2457,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>331°25'52.4"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>61°23'22.3"</t>
+          <t>0°00'00.9"</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2497,17 +2497,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>151°25'52.3"</t>
+          <t>270°00'01.8"</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>61°23'22.3"</t>
+          <t>0°00'00.9"</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2537,22 +2537,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>156°17'29.2"</t>
+          <t>278°23'22.1"</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>66°15'01.1"</t>
+          <t>8°23'22.7"</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4°51'38.8"</t>
+          <t>8°23'21.8"</t>
         </is>
       </c>
     </row>
@@ -2577,22 +2577,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>336°17'33.0"</t>
+          <t>98°23'23.4"</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>66°15'01.1"</t>
+          <t>8°23'22.7"</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4°51'38.8"</t>
+          <t>8°23'21.8"</t>
         </is>
       </c>
     </row>
@@ -2617,17 +2617,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>246°17'30.8"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>66°15'02.1"</t>
+          <t>359°59'59.6"</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2657,17 +2657,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>66°17'33.4"</t>
+          <t>179°59'59.1"</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>66°15'02.1"</t>
+          <t>359°59'59.6"</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>70°14'35.6"</t>
+          <t>189°24'39.8"</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>70°12'05.2"</t>
+          <t>9°24'38.4"</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3°57'03.1"</t>
+          <t>9°24'38.8"</t>
         </is>
       </c>
     </row>
@@ -2737,22 +2737,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>250°14'34.7"</t>
+          <t>9°24'36.9"</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>70°12'05.2"</t>
+          <t>9°24'38.4"</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3°57'03.1"</t>
+          <t>9°24'38.8"</t>
         </is>
       </c>
     </row>
@@ -2777,17 +2777,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>336°17'31.6"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>66°15'01.7"</t>
+          <t>0°00'00.7"</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2817,17 +2817,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>156°17'31.8"</t>
+          <t>270°00'01.3"</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>66°15'01.7"</t>
+          <t>0°00'00.7"</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2857,22 +2857,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>160°14'35.8"</t>
+          <t>279°24'35.2"</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>70°12'04.8"</t>
+          <t>9°24'36.1"</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3°57'03.1"</t>
+          <t>9°24'35.4"</t>
         </is>
       </c>
     </row>
@@ -2897,22 +2897,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>340°14'33.8"</t>
+          <t>99°24'36.9"</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70°12'04.8"</t>
+          <t>9°24'36.1"</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3°57'03.1"</t>
+          <t>9°24'35.4"</t>
         </is>
       </c>
     </row>
@@ -2937,17 +2937,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>250°14'33.3"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>70°12'03.4"</t>
+          <t>0°00'00.3"</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2977,17 +2977,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>70°14'33.4"</t>
+          <t>180°00'00.5"</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>70°12'03.4"</t>
+          <t>0°00'00.3"</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3017,22 +3017,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>68°14'24.8"</t>
+          <t>182°02'12.9"</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>68°11'54.2"</t>
+          <t>2°02'12.9"</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>357°59'50.8"</t>
+          <t>2°02'12.6"</t>
         </is>
       </c>
     </row>
@@ -3057,22 +3057,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>248°14'23.5"</t>
+          <t>2°02'12.8"</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>68°11'54.2"</t>
+          <t>2°02'12.9"</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>357°59'50.8"</t>
+          <t>2°02'12.6"</t>
         </is>
       </c>
     </row>
@@ -3097,17 +3097,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>340°14'34.9"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>70°12'04.1"</t>
+          <t>359°59'59.6"</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>160°14'33.3"</t>
+          <t>269°59'59.1"</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>70°12'04.1"</t>
+          <t>359°59'59.6"</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3177,22 +3177,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>158°14'26.6"</t>
+          <t>272°02'08.1"</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>68°11'57.5"</t>
+          <t>2°02'07.8"</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>357°59'53.4"</t>
+          <t>2°02'08.2"</t>
         </is>
       </c>
     </row>
@@ -3217,22 +3217,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>338°14'28.4"</t>
+          <t>92°02'07.5"</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>68°11'57.5"</t>
+          <t>2°02'07.8"</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>357°59'53.4"</t>
+          <t>2°02'08.2"</t>
         </is>
       </c>
     </row>
@@ -3257,17 +3257,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>248°14'25.9"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>68°11'55.7"</t>
+          <t>359°59'59.5"</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>68°14'25.6"</t>
+          <t>179°59'59.1"</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>68°11'55.7"</t>
+          <t>359°59'59.5"</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>72°17'50.6"</t>
+          <t>207°10'00.7"</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>72°15'21.2"</t>
+          <t>27°10'00.9"</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4°03'25.4"</t>
+          <t>27°10'01.4"</t>
         </is>
       </c>
     </row>
@@ -3377,22 +3377,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>252°17'51.7"</t>
+          <t>27°10'01.1"</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>72°15'21.2"</t>
+          <t>27°10'00.9"</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4°03'25.4"</t>
+          <t>27°10'01.4"</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>338°14'23.5"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>68°11'55.0"</t>
+          <t>0°00'00.1"</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>158°14'26.5"</t>
+          <t>270°00'00.1"</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>68°11'55.0"</t>
+          <t>0°00'00.1"</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3497,22 +3497,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>162°17'49.3"</t>
+          <t>297°10'06.3"</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>72°15'18.9"</t>
+          <t>27°10'05.3"</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4°03'23.9"</t>
+          <t>27°10'05.3"</t>
         </is>
       </c>
     </row>
@@ -3537,22 +3537,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>342°17'48.4"</t>
+          <t>117°10'04.3"</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>72°15'18.9"</t>
+          <t>27°10'05.3"</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4°03'23.9"</t>
+          <t>27°10'05.3"</t>
         </is>
       </c>
     </row>
@@ -3577,17 +3577,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>252°17'50.7"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>72°15'20.3"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3617,17 +3617,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>72°17'49.9"</t>
+          <t>180°00'00.0"</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>72°15'20.3"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3657,22 +3657,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>63°28'37.2"</t>
+          <t>151°14'46.7"</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>63°26'09.3"</t>
+          <t>151°14'46.7"</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>351°10'49.0"</t>
+          <t>151°14'46.7"</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3697,22 +3697,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>243°28'41.3"</t>
+          <t>331°14'46.8"</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>63°26'09.3"</t>
+          <t>151°14'46.7"</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>351°10'49.0"</t>
+          <t>151°14'46.7"</t>
         </is>
       </c>
     </row>
@@ -3737,17 +3737,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>342°17'48.7"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>72°15'18.9"</t>
+          <t>360°00'00.0"</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3777,17 +3777,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>162°17'49.1"</t>
+          <t>269°59'59.9"</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>72°15'18.9"</t>
+          <t>360°00'00.0"</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3817,22 +3817,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>153°28'34.3"</t>
+          <t>241°14'52.2"</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>63°26'04.4"</t>
+          <t>331°14'51.2"</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>351°10'45.5"</t>
+          <t>331°14'51.3"</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3857,29 +3857,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>333°28'34.4"</t>
+          <t>61°14'50.3"</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>63°26'04.4"</t>
+          <t>331°14'51.2"</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>351°10'45.5"</t>
+          <t>331°14'51.3"</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3897,17 +3897,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>243°28'35.5"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>63°26'06.2"</t>
+          <t>0°00'00.9"</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3919,7 +3919,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3937,17 +3937,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>63°28'37.0"</t>
+          <t>180°00'01.8"</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>63°26'06.2"</t>
+          <t>0°00'00.9"</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3959,7 +3959,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>K11</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3977,29 +3977,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>63°28'37.6"</t>
+          <t>190°00'05.6"</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>63°26'07.9"</t>
+          <t>10°00'04.4"</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0°00'01.7"</t>
+          <t>10°00'03.5"</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>K11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4017,29 +4017,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>243°28'38.3"</t>
+          <t>10°00'03.2"</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>63°26'07.9"</t>
+          <t>10°00'04.4"</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>0°00'01.7"</t>
+          <t>10°00'03.5"</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>333°28'36.1"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>63°26'05.8"</t>
+          <t>359°59'59.9"</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4079,7 +4079,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4097,17 +4097,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>153°28'35.6"</t>
+          <t>269°59'59.8"</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>63°26'05.8"</t>
+          <t>359°59'59.9"</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>K11</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4137,29 +4137,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>153°28'35.1"</t>
+          <t>280°00'02.8"</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>63°26'06.1"</t>
+          <t>10°00'03.4"</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0°00'00.3"</t>
+          <t>10°00'03.5"</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4167,32 +4167,992 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>100°00'03.9"</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>10°00'03.4"</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>10°00'03.5"</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0°00'00.2"</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>180°00'00.3"</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0°00'00.2"</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>152°59'32.8"</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-2.92</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>152°59'34.3"</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>152°59'34.1"</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>332°59'35.7"</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-2.92</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>152°59'34.3"</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>152°59'34.1"</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>90°00'00.0"</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>359°59'58.3"</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>269°59'56.7"</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>359°59'58.3"</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>242°59'36.1"</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>332°59'35.2"</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>332°59'36.8"</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>62°59'34.3"</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>332°59'35.2"</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>332°59'36.8"</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0°00'02.0"</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>180°00'04.1"</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0°00'02.0"</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>212°17'07.8"</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>32°17'08.3"</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>32°17'06.2"</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>32°17'08.7"</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>32°17'08.3"</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>32°17'06.2"</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>90°00'00.0"</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0°00'00.2"</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>270°00'00.4"</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0°00'00.2"</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>302°17'05.9"</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>32°17'06.0"</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>32°17'05.8"</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>122°17'06.0"</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>32°17'06.0"</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>32°17'05.8"</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>359°59'59.4"</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>179°59'58.7"</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>359°59'59.4"</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>197°25'09.5"</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>17°25'08.8"</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>17°25'09.4"</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>333°28'37.2"</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-2.11</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>63°26'06.1"</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>0°00'00.3"</t>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>17°25'08.2"</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>17°25'08.8"</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>17°25'09.4"</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>90°00'00.0"</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>0°00'00.7"</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>2</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>270°00'01.5"</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0°00'00.7"</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0°00'00.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>2</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>287°25'08.0"</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>17°25'08.3"</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>17°25'07.6"</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>2</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>107°25'08.6"</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>17°25'08.3"</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>17°25'07.6"</t>
         </is>
       </c>
     </row>
@@ -4207,15 +5167,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
@@ -4274,22 +5234,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>249.9994344026943</v>
+        <v>171.3296782147522</v>
       </c>
       <c r="D2" t="n">
-        <v>249.9991386552885</v>
+        <v>171.3297813283291</v>
       </c>
       <c r="E2" t="n">
-        <v>250.0011299064051</v>
+        <v>171.3299924507707</v>
       </c>
       <c r="F2" t="n">
-        <v>1.991251116550075</v>
+        <v>0.3142360185393045</v>
       </c>
       <c r="G2" t="n">
-        <v>249.9999009881293</v>
+        <v>171.329817331284</v>
       </c>
       <c r="H2" t="n">
-        <v>250.000183879047</v>
+        <v>171.3294933455056</v>
       </c>
     </row>
     <row r="3">
@@ -4304,22 +5264,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>250.0007268623388</v>
+        <v>171.3279221212715</v>
       </c>
       <c r="D3" t="n">
-        <v>250.0002074079613</v>
+        <v>171.3290424872574</v>
       </c>
       <c r="E3" t="n">
-        <v>249.99875264807</v>
+        <v>171.3287467398517</v>
       </c>
       <c r="F3" t="n">
-        <v>1.974214268813057</v>
+        <v>1.120365985968874</v>
       </c>
       <c r="G3" t="n">
-        <v>249.9998956394567</v>
+        <v>171.3285704494602</v>
       </c>
       <c r="H3" t="n">
-        <v>250.000183879047</v>
+        <v>171.3294933455056</v>
       </c>
     </row>
     <row r="4">
@@ -4334,22 +5294,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>249.999743187287</v>
+        <v>171.3307379909682</v>
       </c>
       <c r="D4" t="n">
-        <v>250.0005482843943</v>
+        <v>171.330334946902</v>
       </c>
       <c r="E4" t="n">
-        <v>250.0004443582251</v>
+        <v>171.3298154925244</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8050971072748325</v>
+        <v>0.9224984437992134</v>
       </c>
       <c r="G4" t="n">
-        <v>250.0002452766355</v>
+        <v>171.3302961434648</v>
       </c>
       <c r="H4" t="n">
-        <v>250.000183879047</v>
+        <v>171.3294933455056</v>
       </c>
     </row>
     <row r="5">
@@ -4364,22 +5324,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>250.0001670063624</v>
+        <v>171.3283607326331</v>
       </c>
       <c r="D5" t="n">
-        <v>250.0012510765717</v>
+        <v>171.3293512718502</v>
       </c>
       <c r="E5" t="n">
-        <v>250.000662752966</v>
+        <v>171.3301563689574</v>
       </c>
       <c r="F5" t="n">
-        <v>1.084070209316224</v>
+        <v>1.795636324288807</v>
       </c>
       <c r="G5" t="n">
-        <v>250.0006936119667</v>
+        <v>171.3292894578136</v>
       </c>
       <c r="H5" t="n">
-        <v>250.000183879047</v>
+        <v>171.3294933455056</v>
       </c>
     </row>
     <row r="6">
@@ -4394,22 +5354,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>238.5361636059582</v>
+        <v>125.0653919722548</v>
       </c>
       <c r="D6" t="n">
-        <v>238.536811080139</v>
+        <v>125.0651146203921</v>
       </c>
       <c r="E6" t="n">
-        <v>238.5386898564733</v>
+        <v>125.0661986906014</v>
       </c>
       <c r="F6" t="n">
-        <v>2.526250515103357</v>
+        <v>1.084070209287802</v>
       </c>
       <c r="G6" t="n">
-        <v>238.5372215141902</v>
+        <v>125.0655684277494</v>
       </c>
       <c r="H6" t="n">
-        <v>238.5372246790685</v>
+        <v>125.0649859305766</v>
       </c>
     </row>
     <row r="7">
@@ -4424,22 +5384,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>238.5368953977976</v>
+        <v>125.0656103669958</v>
       </c>
       <c r="D7" t="n">
-        <v>238.5357918199799</v>
+        <v>125.0639023824566</v>
       </c>
       <c r="E7" t="n">
-        <v>238.5372515148942</v>
+        <v>125.0645498566374</v>
       </c>
       <c r="F7" t="n">
-        <v>1.459694914274223</v>
+        <v>1.707984539109475</v>
       </c>
       <c r="G7" t="n">
-        <v>238.5366462442239</v>
+        <v>125.0646875353633</v>
       </c>
       <c r="H7" t="n">
-        <v>238.5372246790685</v>
+        <v>125.0649859305766</v>
       </c>
     </row>
     <row r="8">
@@ -4454,22 +5414,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>238.5375133670806</v>
+        <v>125.0664286329718</v>
       </c>
       <c r="D8" t="n">
-        <v>238.536488662365</v>
+        <v>125.064634174296</v>
       </c>
       <c r="E8" t="n">
-        <v>238.5358643543692</v>
+        <v>125.0635305964784</v>
       </c>
       <c r="F8" t="n">
-        <v>1.649012711482101</v>
+        <v>2.898036493377276</v>
       </c>
       <c r="G8" t="n">
-        <v>238.5366221279382</v>
+        <v>125.0648644679154</v>
       </c>
       <c r="H8" t="n">
-        <v>238.5372246790685</v>
+        <v>125.0649859305766</v>
       </c>
     </row>
     <row r="9">
@@ -4484,22 +5444,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>238.538242066319</v>
+        <v>125.0649902913926</v>
       </c>
       <c r="D9" t="n">
-        <v>238.5391324644229</v>
+        <v>125.0652521435791</v>
       </c>
       <c r="E9" t="n">
-        <v>238.5378519590232</v>
+        <v>125.0642274388634</v>
       </c>
       <c r="F9" t="n">
-        <v>1.280505399705589</v>
+        <v>1.024704715675284</v>
       </c>
       <c r="G9" t="n">
-        <v>238.5384088299217</v>
+        <v>125.0648232912784</v>
       </c>
       <c r="H9" t="n">
-        <v>238.5372246790685</v>
+        <v>125.0649859305766</v>
       </c>
     </row>
     <row r="10">
@@ -4514,22 +5474,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>269.2580357083636</v>
+        <v>134.9502450915442</v>
       </c>
       <c r="D10" t="n">
-        <v>269.2606712090646</v>
+        <v>134.9526228034941</v>
       </c>
       <c r="E10" t="n">
-        <v>269.2583345191028</v>
+        <v>134.953513201598</v>
       </c>
       <c r="F10" t="n">
-        <v>2.635500700989724</v>
+        <v>3.268110053767259</v>
       </c>
       <c r="G10" t="n">
-        <v>269.259013812177</v>
+        <v>134.9521270322121</v>
       </c>
       <c r="H10" t="n">
-        <v>269.2583940326871</v>
+        <v>134.9520033228584</v>
       </c>
     </row>
     <row r="11">
@@ -4544,22 +5504,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>269.2588768496997</v>
+        <v>134.9522326961983</v>
       </c>
       <c r="D11" t="n">
-        <v>269.2596249919281</v>
+        <v>134.9513849263448</v>
       </c>
       <c r="E11" t="n">
-        <v>269.2579569064043</v>
+        <v>134.9540204270458</v>
       </c>
       <c r="F11" t="n">
-        <v>1.668085523874652</v>
+        <v>2.635500700989724</v>
       </c>
       <c r="G11" t="n">
-        <v>269.2588195826774</v>
+        <v>134.9525460165296</v>
       </c>
       <c r="H11" t="n">
-        <v>269.2583940326871</v>
+        <v>134.9520033228584</v>
       </c>
     </row>
     <row r="12">
@@ -4574,22 +5534,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>269.256420231476</v>
+        <v>134.951683737084</v>
       </c>
       <c r="D12" t="n">
-        <v>269.2587119215781</v>
+        <v>134.9522260676808</v>
       </c>
       <c r="E12" t="n">
-        <v>269.2561473988183</v>
+        <v>134.9529742099093</v>
       </c>
       <c r="F12" t="n">
-        <v>2.564522759826104</v>
+        <v>1.290472825388633</v>
       </c>
       <c r="G12" t="n">
-        <v>269.2570931839575</v>
+        <v>134.9522946715581</v>
       </c>
       <c r="H12" t="n">
-        <v>269.2583940326871</v>
+        <v>134.9520033228584</v>
       </c>
     </row>
     <row r="13">
@@ -4604,22 +5564,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>269.2573547414996</v>
+        <v>134.9513061243854</v>
       </c>
       <c r="D13" t="n">
-        <v>269.2596516028237</v>
+        <v>134.9497694494572</v>
       </c>
       <c r="E13" t="n">
-        <v>269.2589423114856</v>
+        <v>134.9520611395593</v>
       </c>
       <c r="F13" t="n">
-        <v>2.296861324111887</v>
+        <v>2.291690102168786</v>
       </c>
       <c r="G13" t="n">
-        <v>269.2586495519363</v>
+        <v>134.951045571134</v>
       </c>
       <c r="H13" t="n">
-        <v>269.2583940326871</v>
+        <v>134.9520033228584</v>
       </c>
     </row>
     <row r="14">
@@ -4634,22 +5594,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>259.4226117779279</v>
+        <v>149.5835102349138</v>
       </c>
       <c r="D14" t="n">
-        <v>259.4206996485031</v>
+        <v>149.5847175775951</v>
       </c>
       <c r="E14" t="n">
-        <v>259.4208570671505</v>
+        <v>149.5870144389192</v>
       </c>
       <c r="F14" t="n">
-        <v>1.912129424795239</v>
+        <v>3.504204005423617</v>
       </c>
       <c r="G14" t="n">
-        <v>259.4213894978605</v>
+        <v>149.585080750476</v>
       </c>
       <c r="H14" t="n">
-        <v>259.4222028208943</v>
+        <v>149.5850999747892</v>
       </c>
     </row>
     <row r="15">
@@ -4664,22 +5624,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>259.4208998025648</v>
+        <v>149.586305147581</v>
       </c>
       <c r="D15" t="n">
-        <v>259.4244245194303</v>
+        <v>149.5857795492917</v>
       </c>
       <c r="E15" t="n">
-        <v>259.422144616495</v>
+        <v>149.5838674198668</v>
       </c>
       <c r="F15" t="n">
-        <v>3.524716865513255</v>
+        <v>2.437727714180937</v>
       </c>
       <c r="G15" t="n">
-        <v>259.4224896461633</v>
+        <v>149.5853173722465</v>
       </c>
       <c r="H15" t="n">
-        <v>259.4222028208943</v>
+        <v>149.5850999747892</v>
       </c>
     </row>
     <row r="16">
@@ -4694,22 +5654,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>259.4200570219994</v>
+        <v>149.5840248385142</v>
       </c>
       <c r="D16" t="n">
-        <v>259.4226156734802</v>
+        <v>149.5840675739286</v>
       </c>
       <c r="E16" t="n">
-        <v>259.4238741168383</v>
+        <v>149.587592290794</v>
       </c>
       <c r="F16" t="n">
-        <v>3.817094838950652</v>
+        <v>3.567452279867211</v>
       </c>
       <c r="G16" t="n">
-        <v>259.4221822707726</v>
+        <v>149.5852282344123</v>
       </c>
       <c r="H16" t="n">
-        <v>259.4222028208943</v>
+        <v>149.5850999747892</v>
       </c>
     </row>
     <row r="17">
@@ -4724,22 +5684,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>259.4234557577832</v>
+        <v>149.5853123878587</v>
       </c>
       <c r="D17" t="n">
-        <v>259.4229701886132</v>
+        <v>149.5832247933631</v>
       </c>
       <c r="E17" t="n">
-        <v>259.4218236599463</v>
+        <v>149.5857834448439</v>
       </c>
       <c r="F17" t="n">
-        <v>1.632097836932189</v>
+        <v>2.558651480853769</v>
       </c>
       <c r="G17" t="n">
-        <v>259.422749868781</v>
+        <v>149.5847735420219</v>
       </c>
       <c r="H17" t="n">
-        <v>259.4222028208943</v>
+        <v>149.5850999747892</v>
       </c>
     </row>
     <row r="18">
@@ -4754,22 +5714,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>250.6006838238786</v>
+        <v>158.9520222559333</v>
       </c>
       <c r="D18" t="n">
-        <v>250.5994530295615</v>
+        <v>158.9516038968782</v>
       </c>
       <c r="E18" t="n">
-        <v>250.6009181203943</v>
+        <v>158.9511183277082</v>
       </c>
       <c r="F18" t="n">
-        <v>1.465090832766691</v>
+        <v>0.9039282250853375</v>
       </c>
       <c r="G18" t="n">
-        <v>250.6003516579448</v>
+        <v>158.9515814935066</v>
       </c>
       <c r="H18" t="n">
-        <v>250.5998753079505</v>
+        <v>158.9510395012817</v>
       </c>
     </row>
     <row r="19">
@@ -4784,22 +5744,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>250.5998914451755</v>
+        <v>158.9499717990413</v>
       </c>
       <c r="D19" t="n">
-        <v>250.5996636995412</v>
+        <v>158.9519856615972</v>
       </c>
       <c r="E19" t="n">
-        <v>250.6002755718566</v>
+        <v>158.9507548672801</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6118723154031613</v>
+        <v>2.013862555912738</v>
       </c>
       <c r="G19" t="n">
-        <v>250.5999435721911</v>
+        <v>158.9509041093062</v>
       </c>
       <c r="H19" t="n">
-        <v>250.5998753079505</v>
+        <v>158.9510395012817</v>
       </c>
     </row>
     <row r="20">
@@ -4814,22 +5774,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>250.5982383166882</v>
+        <v>158.9522199581128</v>
       </c>
       <c r="D20" t="n">
-        <v>250.5982190269745</v>
+        <v>158.951193282894</v>
       </c>
       <c r="E20" t="n">
-        <v>250.6006322646659</v>
+        <v>158.9509655372598</v>
       </c>
       <c r="F20" t="n">
-        <v>2.413237691342829</v>
+        <v>1.254420853058491</v>
       </c>
       <c r="G20" t="n">
-        <v>250.5990298694429</v>
+        <v>158.9514595927556</v>
       </c>
       <c r="H20" t="n">
-        <v>250.5998753079505</v>
+        <v>158.9510395012817</v>
       </c>
     </row>
     <row r="21">
@@ -4844,22 +5804,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>250.599780471831</v>
+        <v>158.9515774095752</v>
       </c>
       <c r="D21" t="n">
-        <v>250.6006161767641</v>
+        <v>158.9495401544067</v>
       </c>
       <c r="E21" t="n">
-        <v>250.6001317480748</v>
+        <v>158.9495208646931</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8357049331095823</v>
+        <v>2.056544882094613</v>
       </c>
       <c r="G21" t="n">
-        <v>250.6001761322233</v>
+        <v>158.9502128095583</v>
       </c>
       <c r="H21" t="n">
-        <v>250.5998753079505</v>
+        <v>158.9510395012817</v>
       </c>
     </row>
     <row r="22">
@@ -4874,22 +5834,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>273.1303781616347</v>
+        <v>130.5243290533575</v>
       </c>
       <c r="D22" t="n">
-        <v>273.1298207007438</v>
+        <v>130.5234772605227</v>
       </c>
       <c r="E22" t="n">
-        <v>273.1278221987736</v>
+        <v>130.5243129654558</v>
       </c>
       <c r="F22" t="n">
-        <v>2.555962861151784</v>
+        <v>0.8517928348510395</v>
       </c>
       <c r="G22" t="n">
-        <v>273.1293403537174</v>
+        <v>130.5240397597787</v>
       </c>
       <c r="H22" t="n">
-        <v>273.1293452679554</v>
+        <v>130.5227940360481</v>
       </c>
     </row>
     <row r="23">
@@ -4904,22 +5864,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>273.1295822725099</v>
+        <v>130.5238285367664</v>
       </c>
       <c r="D23" t="n">
-        <v>273.1285363487251</v>
+        <v>130.5233509982065</v>
       </c>
       <c r="E23" t="n">
-        <v>273.128449524035</v>
+        <v>130.5227935373156</v>
       </c>
       <c r="F23" t="n">
-        <v>1.132748474901746</v>
+        <v>1.034999450865826</v>
       </c>
       <c r="G23" t="n">
-        <v>273.1288560484234</v>
+        <v>130.5233243574295</v>
       </c>
       <c r="H23" t="n">
-        <v>273.1293452679554</v>
+        <v>130.5227940360481</v>
       </c>
     </row>
     <row r="24">
@@ -4934,22 +5894,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>273.1301572049059</v>
+        <v>130.5207950353453</v>
       </c>
       <c r="D24" t="n">
-        <v>273.1290515125729</v>
+        <v>130.5225551090817</v>
       </c>
       <c r="E24" t="n">
-        <v>273.129842540051</v>
+        <v>130.5215091852968</v>
       </c>
       <c r="F24" t="n">
-        <v>1.105692332998842</v>
+        <v>1.760073736392087</v>
       </c>
       <c r="G24" t="n">
-        <v>273.1296837525099</v>
+        <v>130.5216197765746</v>
       </c>
       <c r="H24" t="n">
-        <v>273.1293452679554</v>
+        <v>130.5227940360481</v>
       </c>
     </row>
     <row r="25">
@@ -4964,22 +5924,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>273.1300228477116</v>
+        <v>130.5214223606067</v>
       </c>
       <c r="D25" t="n">
-        <v>273.1299213302732</v>
+        <v>130.5231300414776</v>
       </c>
       <c r="E25" t="n">
-        <v>273.1285585735271</v>
+        <v>130.5220243491446</v>
       </c>
       <c r="F25" t="n">
-        <v>1.46427418451367</v>
+        <v>1.707680870850936</v>
       </c>
       <c r="G25" t="n">
-        <v>273.1295009171707</v>
+        <v>130.5221922504096</v>
       </c>
       <c r="H25" t="n">
-        <v>273.1293452679554</v>
+        <v>130.5227940360481</v>
       </c>
     </row>
     <row r="26">
@@ -4994,22 +5954,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>265.7060827103276</v>
+        <v>190.6033619928614</v>
       </c>
       <c r="D26" t="n">
-        <v>265.7066406783247</v>
+        <v>190.603542300522</v>
       </c>
       <c r="E26" t="n">
-        <v>265.7059606866754</v>
+        <v>190.6034407830836</v>
       </c>
       <c r="F26" t="n">
-        <v>0.679991649292333</v>
+        <v>0.1803076606279319</v>
       </c>
       <c r="G26" t="n">
-        <v>265.7062280251092</v>
+        <v>190.6034483588223</v>
       </c>
       <c r="H26" t="n">
-        <v>265.7063842434742</v>
+        <v>190.6029696408255</v>
       </c>
     </row>
     <row r="27">
@@ -5024,22 +5984,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>265.7061908109842</v>
+        <v>190.6020780263375</v>
       </c>
       <c r="D27" t="n">
-        <v>265.7058194903726</v>
+        <v>190.6030027263628</v>
       </c>
       <c r="E27" t="n">
-        <v>265.705464886374</v>
+        <v>190.6035606943598</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7259246101511962</v>
+        <v>1.482668022362077</v>
       </c>
       <c r="G27" t="n">
-        <v>265.7058250625769</v>
+        <v>190.6028804823534</v>
       </c>
       <c r="H27" t="n">
-        <v>265.7063842434742</v>
+        <v>190.6029696408255</v>
       </c>
     </row>
     <row r="28">
@@ -5054,22 +6014,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>265.7083613107006</v>
+        <v>190.6028807027105</v>
       </c>
       <c r="D28" t="n">
-        <v>265.7033318850615</v>
+        <v>190.6031108270194</v>
       </c>
       <c r="E28" t="n">
-        <v>265.7051685448115</v>
+        <v>190.6027395064077</v>
       </c>
       <c r="F28" t="n">
-        <v>5.029425639065721</v>
+        <v>0.3713206116344736</v>
       </c>
       <c r="G28" t="n">
-        <v>265.7056205801912</v>
+        <v>190.6029103453792</v>
       </c>
       <c r="H28" t="n">
-        <v>265.7063842434742</v>
+        <v>190.6029696408255</v>
       </c>
     </row>
     <row r="29">
@@ -5084,22 +6044,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>265.7087440897724</v>
+        <v>190.6023849024092</v>
       </c>
       <c r="D29" t="n">
-        <v>265.706883052034</v>
+        <v>190.6052813267357</v>
       </c>
       <c r="E29" t="n">
-        <v>265.7079627762524</v>
+        <v>190.6002519010967</v>
       </c>
       <c r="F29" t="n">
-        <v>1.861037738365212</v>
+        <v>5.029425639037299</v>
       </c>
       <c r="G29" t="n">
-        <v>265.7078633060196</v>
+        <v>190.6026393767472</v>
       </c>
       <c r="H29" t="n">
-        <v>265.7063842434742</v>
+        <v>190.6029696408255</v>
       </c>
     </row>
     <row r="30">
@@ -5114,22 +6074,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>269.2604292826456</v>
+        <v>123.7237130036129</v>
       </c>
       <c r="D30" t="n">
-        <v>269.2581152679006</v>
+        <v>123.7272885485738</v>
       </c>
       <c r="E30" t="n">
-        <v>269.2599118164789</v>
+        <v>123.7254275108354</v>
       </c>
       <c r="F30" t="n">
-        <v>2.314014745024906</v>
+        <v>3.575544960924049</v>
       </c>
       <c r="G30" t="n">
-        <v>269.2594854556751</v>
+        <v>123.7254763543407</v>
       </c>
       <c r="H30" t="n">
-        <v>269.2588004827543</v>
+        <v>123.7256604726509</v>
       </c>
     </row>
     <row r="31">
@@ -5144,22 +6104,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>269.2559540489731</v>
+        <v>123.7265072350538</v>
       </c>
       <c r="D31" t="n">
-        <v>269.2589950159403</v>
+        <v>123.7273384964503</v>
       </c>
       <c r="E31" t="n">
-        <v>269.2588332018733</v>
+        <v>123.7250244817053</v>
       </c>
       <c r="F31" t="n">
-        <v>3.040966967262193</v>
+        <v>2.314014745010695</v>
       </c>
       <c r="G31" t="n">
-        <v>269.2579274222622</v>
+        <v>123.7262900710698</v>
       </c>
       <c r="H31" t="n">
-        <v>269.2588004827543</v>
+        <v>123.7256604726509</v>
       </c>
     </row>
     <row r="32">
@@ -5174,22 +6134,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>269.2574006972206</v>
+        <v>123.7268210302835</v>
       </c>
       <c r="D32" t="n">
-        <v>269.2600763322647</v>
+        <v>123.7228632627777</v>
       </c>
       <c r="E32" t="n">
-        <v>269.2594743050744</v>
+        <v>123.725904229745</v>
       </c>
       <c r="F32" t="n">
-        <v>2.675635044056435</v>
+        <v>3.957767505809784</v>
       </c>
       <c r="G32" t="n">
-        <v>269.2589837781866</v>
+        <v>123.7251961742688</v>
       </c>
       <c r="H32" t="n">
-        <v>269.2588004827543</v>
+        <v>123.7256604726509</v>
       </c>
     </row>
     <row r="33">
@@ -5204,22 +6164,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>269.2585600412746</v>
+        <v>123.725742415678</v>
       </c>
       <c r="D33" t="n">
-        <v>269.2581417758013</v>
+        <v>123.7243099110253</v>
       </c>
       <c r="E33" t="n">
-        <v>269.2597140076035</v>
+        <v>123.7269855460693</v>
       </c>
       <c r="F33" t="n">
-        <v>1.572231802128954</v>
+        <v>2.675635044056435</v>
       </c>
       <c r="G33" t="n">
-        <v>269.2588052748931</v>
+        <v>123.7256792909242</v>
       </c>
       <c r="H33" t="n">
-        <v>269.2588004827543</v>
+        <v>123.7256604726509</v>
       </c>
     </row>
     <row r="34">
@@ -5234,22 +6194,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>262.4864180580219</v>
+        <v>143.390194796317</v>
       </c>
       <c r="D34" t="n">
-        <v>262.48816421222</v>
+        <v>143.3892805325172</v>
       </c>
       <c r="E34" t="n">
-        <v>262.4882803424425</v>
+        <v>143.3888622670439</v>
       </c>
       <c r="F34" t="n">
-        <v>1.862284420610649</v>
+        <v>1.332529273071259</v>
       </c>
       <c r="G34" t="n">
-        <v>262.4876208708948</v>
+        <v>143.3894458652927</v>
       </c>
       <c r="H34" t="n">
-        <v>262.4877771880526</v>
+        <v>143.388990578176</v>
       </c>
     </row>
     <row r="35">
@@ -5264,22 +6224,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>262.4887295909769</v>
+        <v>143.390434498846</v>
       </c>
       <c r="D35" t="n">
-        <v>262.4879757810253</v>
+        <v>143.3872839378559</v>
       </c>
       <c r="E35" t="n">
-        <v>262.4876339263756</v>
+        <v>143.3890300920541</v>
       </c>
       <c r="F35" t="n">
-        <v>1.095664601336921</v>
+        <v>3.150560990150097</v>
       </c>
       <c r="G35" t="n">
-        <v>262.4881130994593</v>
+        <v>143.388916176252</v>
       </c>
       <c r="H35" t="n">
-        <v>262.4877771880526</v>
+        <v>143.388990578176</v>
       </c>
     </row>
     <row r="36">
@@ -5294,22 +6254,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>262.4867685785847</v>
+        <v>143.3891462222765</v>
       </c>
       <c r="D36" t="n">
-        <v>262.4882173150687</v>
+        <v>143.3895954708109</v>
       </c>
       <c r="E36" t="n">
-        <v>262.4885189364234</v>
+        <v>143.3888416608593</v>
       </c>
       <c r="F36" t="n">
-        <v>1.750357838716354</v>
+        <v>0.7538099516466445</v>
       </c>
       <c r="G36" t="n">
-        <v>262.4878349433589</v>
+        <v>143.3891944513156</v>
       </c>
       <c r="H36" t="n">
-        <v>262.4877771880526</v>
+        <v>143.388990578176</v>
       </c>
     </row>
     <row r="37">
@@ -5324,28 +6284,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>262.4861870116756</v>
+        <v>143.3884998062096</v>
       </c>
       <c r="D37" t="n">
-        <v>262.4888648860446</v>
+        <v>143.3876344584187</v>
       </c>
       <c r="E37" t="n">
-        <v>262.4875676177732</v>
+        <v>143.3890831949027</v>
       </c>
       <c r="F37" t="n">
-        <v>2.677874368941957</v>
+        <v>1.448736484007895</v>
       </c>
       <c r="G37" t="n">
-        <v>262.4875398384978</v>
+        <v>143.3884058198437</v>
       </c>
       <c r="H37" t="n">
-        <v>262.4877771880526</v>
+        <v>143.388990578176</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>K9-G</t>
+          <t>K9-K10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5354,28 +6314,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>223.6062562874748</v>
+        <v>163.7441216549487</v>
       </c>
       <c r="D38" t="n">
-        <v>223.6072594638994</v>
+        <v>163.7417897302008</v>
       </c>
       <c r="E38" t="n">
-        <v>223.6057151358536</v>
+        <v>163.7444676045698</v>
       </c>
       <c r="F38" t="n">
-        <v>1.544328045724797</v>
+        <v>2.677874368941957</v>
       </c>
       <c r="G38" t="n">
-        <v>223.6064102957426</v>
+        <v>163.7434596632397</v>
       </c>
       <c r="H38" t="n">
-        <v>223.6066970318542</v>
+        <v>163.7434618707985</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>K9-G</t>
+          <t>K9-K10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5384,28 +6344,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>223.6059547757879</v>
+        <v>163.7431703362984</v>
       </c>
       <c r="D39" t="n">
-        <v>223.6058113368083</v>
+        <v>163.7431562241547</v>
       </c>
       <c r="E39" t="n">
-        <v>223.6087077843794</v>
+        <v>163.7441594005793</v>
       </c>
       <c r="F39" t="n">
-        <v>2.896447571089311</v>
+        <v>1.00317642460368</v>
       </c>
       <c r="G39" t="n">
-        <v>223.6068246323252</v>
+        <v>163.7434953203442</v>
       </c>
       <c r="H39" t="n">
-        <v>223.6066970318542</v>
+        <v>163.7434618707985</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>K9-G</t>
+          <t>K9-K10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5414,28 +6374,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>223.6058270144835</v>
+        <v>163.7426150725336</v>
       </c>
       <c r="D40" t="n">
-        <v>223.6072618314378</v>
+        <v>163.7428547124679</v>
       </c>
       <c r="E40" t="n">
-        <v>223.606452882359</v>
+        <v>163.7427112734883</v>
       </c>
       <c r="F40" t="n">
-        <v>1.434816954315465</v>
+        <v>0.2396399343069788</v>
       </c>
       <c r="G40" t="n">
-        <v>223.6065139094268</v>
+        <v>163.7427270194966</v>
       </c>
       <c r="H40" t="n">
-        <v>223.6066970318542</v>
+        <v>163.7434618707985</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>K9-G</t>
+          <t>K9-K10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5444,22 +6404,382 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>223.6085586890833</v>
+        <v>163.7456077210594</v>
       </c>
       <c r="D41" t="n">
-        <v>223.6064436939352</v>
+        <v>163.7427269511634</v>
       </c>
       <c r="E41" t="n">
-        <v>223.6061154867477</v>
+        <v>163.7441617681177</v>
       </c>
       <c r="F41" t="n">
-        <v>2.443202335683736</v>
+        <v>2.88076989596675</v>
       </c>
       <c r="G41" t="n">
-        <v>223.6070392899221</v>
+        <v>163.7441654801135</v>
       </c>
       <c r="H41" t="n">
-        <v>223.6066970318542</v>
+        <v>163.7434618707985</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>K10-K11</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>往测</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>135.174353568515</v>
+      </c>
+      <c r="D42" t="n">
+        <v>135.1764593752393</v>
+      </c>
+      <c r="E42" t="n">
+        <v>135.1743443800912</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.114995148104981</v>
+      </c>
+      <c r="G42" t="n">
+        <v>135.1750524412818</v>
+      </c>
+      <c r="H42" t="n">
+        <v>135.1748654285916</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>K10-K11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>往测</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>135.1740161729037</v>
+      </c>
+      <c r="D43" t="n">
+        <v>135.1737888854385</v>
+      </c>
+      <c r="E43" t="n">
+        <v>135.175447554403</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.658668964495291</v>
+      </c>
+      <c r="G43" t="n">
+        <v>135.1744175375817</v>
+      </c>
+      <c r="H43" t="n">
+        <v>135.1748654285916</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>K10-K11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>返测</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>135.1732683595656</v>
+      </c>
+      <c r="D44" t="n">
+        <v>135.1749217200593</v>
+      </c>
+      <c r="E44" t="n">
+        <v>135.1759588708978</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.690511332218648</v>
+      </c>
+      <c r="G44" t="n">
+        <v>135.1747163168409</v>
+      </c>
+      <c r="H44" t="n">
+        <v>135.1748654285916</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>K10-K11</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>返测</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>135.1745531801409</v>
+      </c>
+      <c r="D45" t="n">
+        <v>135.1747151573088</v>
+      </c>
+      <c r="E45" t="n">
+        <v>135.1765579185363</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.004738395356753</v>
+      </c>
+      <c r="G45" t="n">
+        <v>135.175275418662</v>
+      </c>
+      <c r="H45" t="n">
+        <v>135.1748654285916</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>K11-K12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>往测</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>195.8874557181627</v>
+      </c>
+      <c r="D46" t="n">
+        <v>195.8861797424851</v>
+      </c>
+      <c r="E46" t="n">
+        <v>195.8884430781895</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.263335704355995</v>
+      </c>
+      <c r="G46" t="n">
+        <v>195.8873595129457</v>
+      </c>
+      <c r="H46" t="n">
+        <v>195.8868156270867</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>K11-K12</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>往测</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>195.8866615751343</v>
+      </c>
+      <c r="D47" t="n">
+        <v>195.8881075964623</v>
+      </c>
+      <c r="E47" t="n">
+        <v>195.8859086625125</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.19893394984183</v>
+      </c>
+      <c r="G47" t="n">
+        <v>195.8868926113697</v>
+      </c>
+      <c r="H47" t="n">
+        <v>195.8868156270867</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>K11-K12</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>返测</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>195.884131277772</v>
+      </c>
+      <c r="D48" t="n">
+        <v>195.8878838234036</v>
+      </c>
+      <c r="E48" t="n">
+        <v>195.8865974751284</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.752545631613202</v>
+      </c>
+      <c r="G48" t="n">
+        <v>195.8862041921013</v>
+      </c>
+      <c r="H48" t="n">
+        <v>195.8868156270867</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>K11-K12</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>返测</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>195.8878027284113</v>
+      </c>
+      <c r="D49" t="n">
+        <v>195.8872006874836</v>
+      </c>
+      <c r="E49" t="n">
+        <v>195.8854151598953</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.387568516041938</v>
+      </c>
+      <c r="G49" t="n">
+        <v>195.8868061919301</v>
+      </c>
+      <c r="H49" t="n">
+        <v>195.8868156270867</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>K12-G</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>往测</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>196.5516013950617</v>
+      </c>
+      <c r="D50" t="n">
+        <v>196.5504798227117</v>
+      </c>
+      <c r="E50" t="n">
+        <v>196.5520042238047</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.524401093007555</v>
+      </c>
+      <c r="G50" t="n">
+        <v>196.5513618138594</v>
+      </c>
+      <c r="H50" t="n">
+        <v>196.5510278543762</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>K12-G</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>往测</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>196.5501205504498</v>
+      </c>
+      <c r="D51" t="n">
+        <v>196.552301812606</v>
+      </c>
+      <c r="E51" t="n">
+        <v>196.550173935829</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.181262156199182</v>
+      </c>
+      <c r="G51" t="n">
+        <v>196.5508654329616</v>
+      </c>
+      <c r="H51" t="n">
+        <v>196.5510278543762</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>K12-G</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>返测</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>196.5508202116671</v>
+      </c>
+      <c r="D52" t="n">
+        <v>196.5526524890842</v>
+      </c>
+      <c r="E52" t="n">
+        <v>196.5514117719116</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.832277417094019</v>
+      </c>
+      <c r="G52" t="n">
+        <v>196.5516281575543</v>
+      </c>
+      <c r="H52" t="n">
+        <v>196.5510278543762</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>K12-G</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>返测</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>196.5511749922167</v>
+      </c>
+      <c r="D53" t="n">
+        <v>196.5507666214491</v>
+      </c>
+      <c r="E53" t="n">
+        <v>196.5488264257221</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.34856649464632</v>
+      </c>
+      <c r="G53" t="n">
+        <v>196.5502560131293</v>
+      </c>
+      <c r="H53" t="n">
+        <v>196.5510278543762</v>
       </c>
     </row>
   </sheetData>
@@ -5473,11 +6793,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -5540,10 +6860,10 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>10000</v>
+        <v>101.5871</v>
       </c>
       <c r="H2" t="n">
-        <v>5000</v>
+        <v>271.6248</v>
       </c>
     </row>
     <row r="3">
@@ -5554,22 +6874,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>233°07'50.3"</t>
+          <t>168°21'47.3"</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>53°07'50.3"</t>
+          <t>57°51'26.8"</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>250.000183879047</v>
+        <v>171.3294933455056</v>
       </c>
       <c r="E3" t="n">
-        <v>149.9982560268532</v>
+        <v>91.15201201463836</v>
       </c>
       <c r="F3" t="n">
-        <v>200.0015378152376</v>
+        <v>145.0693144524743</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -5582,7 +6902,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>183°50'45.5"</t>
+          <t>165°41'17.0"</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -5590,10 +6910,10 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>10149.99825602685</v>
+        <v>192.7391120146384</v>
       </c>
       <c r="H4" t="n">
-        <v>5200.001537815237</v>
+        <v>416.6941144524743</v>
       </c>
     </row>
     <row r="5">
@@ -5604,22 +6924,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>183°50'45.5"</t>
+          <t>165°41'17.0"</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56°58'35.8"</t>
+          <t>43°32'43.8"</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>238.5372246790685</v>
+        <v>125.0649859305766</v>
       </c>
       <c r="E5" t="n">
-        <v>129.9983751601969</v>
+        <v>90.65055137922391</v>
       </c>
       <c r="F5" t="n">
-        <v>200.0010750303636</v>
+        <v>86.1610598847183</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -5632,7 +6952,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>191°13'22.1"</t>
+          <t>204°35'20.4"</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -5640,10 +6960,10 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>10279.99663118705</v>
+        <v>283.3896633938623</v>
       </c>
       <c r="H6" t="n">
-        <v>5400.002612845601</v>
+        <v>502.8551743371926</v>
       </c>
     </row>
     <row r="7">
@@ -5654,22 +6974,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>191°13'22.1"</t>
+          <t>204°35'20.4"</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>68°11'57.9"</t>
+          <t>68°08'04.2"</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>269.2583940326871</v>
+        <v>134.9520033228584</v>
       </c>
       <c r="E7" t="n">
-        <v>99.99648708430313</v>
+        <v>50.26005814835942</v>
       </c>
       <c r="F7" t="n">
-        <v>250.0015706507873</v>
+        <v>125.2436415782307</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -5682,7 +7002,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>174°14'56.7"</t>
+          <t>136°00'14.0"</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -5690,10 +7010,10 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>10379.99311827135</v>
+        <v>333.6497215422217</v>
       </c>
       <c r="H8" t="n">
-        <v>5650.004183496389</v>
+        <v>628.0988159154233</v>
       </c>
     </row>
     <row r="9">
@@ -5704,22 +7024,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>174°14'56.7"</t>
+          <t>136°00'14.0"</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>62°26'54.6"</t>
+          <t>24°08'18.2"</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>259.4222028208943</v>
+        <v>149.5850999747892</v>
       </c>
       <c r="E9" t="n">
-        <v>119.9946304345739</v>
+        <v>136.5054299663758</v>
       </c>
       <c r="F9" t="n">
-        <v>230.0025390801485</v>
+        <v>61.17164150292636</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -5732,7 +7052,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>178°56'31.8"</t>
+          <t>177°58'47.4"</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -5740,10 +7060,10 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>10499.98774870593</v>
+        <v>470.1551515085975</v>
       </c>
       <c r="H10" t="n">
-        <v>5880.006722576537</v>
+        <v>689.2704574183497</v>
       </c>
     </row>
     <row r="11">
@@ -5754,22 +7074,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>178°56'31.8"</t>
+          <t>177°58'47.4"</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>61°23'26.4"</t>
+          <t>22°07'05.7"</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>250.5998753079505</v>
+        <v>158.9510395012816</v>
       </c>
       <c r="E11" t="n">
-        <v>119.9959456258278</v>
+        <v>147.2536424805108</v>
       </c>
       <c r="F11" t="n">
-        <v>220.0028875667857</v>
+        <v>59.84812223253043</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -5782,7 +7102,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>184°51'38.4"</t>
+          <t>188°23'22.7"</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -5790,10 +7110,10 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>10619.98369433176</v>
+        <v>617.4087939891083</v>
       </c>
       <c r="H12" t="n">
-        <v>6100.009610143323</v>
+        <v>749.1185796508801</v>
       </c>
     </row>
     <row r="13">
@@ -5804,22 +7124,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>184°51'38.4"</t>
+          <t>188°23'22.7"</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>66°15'04.8"</t>
+          <t>30°30'28.3"</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>273.1293452679553</v>
+        <v>130.5227940360481</v>
       </c>
       <c r="E13" t="n">
-        <v>109.996067416877</v>
+        <v>112.4531460103301</v>
       </c>
       <c r="F13" t="n">
-        <v>250.0010087966122</v>
+        <v>66.26077056113975</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -5832,7 +7152,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>183°57'03.1"</t>
+          <t>189°24'37.1"</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -5840,10 +7160,10 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>10729.97976174863</v>
+        <v>729.8619399994384</v>
       </c>
       <c r="H14" t="n">
-        <v>6350.010618939935</v>
+        <v>815.3793502120199</v>
       </c>
     </row>
     <row r="15">
@@ -5854,22 +7174,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>183°57'03.1"</t>
+          <t>189°24'37.1"</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>70°12'07.9"</t>
+          <t>39°55'05.4"</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>265.7063842434742</v>
+        <v>190.6029696408255</v>
       </c>
       <c r="E15" t="n">
-        <v>89.99521451598818</v>
+        <v>146.1851623068641</v>
       </c>
       <c r="F15" t="n">
-        <v>250.0014879794959</v>
+        <v>122.3085866046095</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -5882,7 +7202,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>177°59'52.1"</t>
+          <t>182°02'10.4"</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -5890,10 +7210,10 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>10819.97497626462</v>
+        <v>876.0471023063025</v>
       </c>
       <c r="H16" t="n">
-        <v>6600.012106919431</v>
+        <v>937.6879368166293</v>
       </c>
     </row>
     <row r="17">
@@ -5904,22 +7224,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>177°59'52.1"</t>
+          <t>182°02'10.4"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>68°12'00.1"</t>
+          <t>41°57'15.9"</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>269.2588004827543</v>
+        <v>123.7256604726508</v>
       </c>
       <c r="E17" t="n">
-        <v>99.99397782401354</v>
+        <v>92.01193481762328</v>
       </c>
       <c r="F17" t="n">
-        <v>250.0030120545398</v>
+        <v>82.71543332722811</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -5932,7 +7252,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>184°03'24.6"</t>
+          <t>207°10'03.3"</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -5940,10 +7260,10 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>10919.96895408863</v>
+        <v>968.0590371239257</v>
       </c>
       <c r="H18" t="n">
-        <v>6850.015118973971</v>
+        <v>1020.403370143857</v>
       </c>
     </row>
     <row r="19">
@@ -5954,22 +7274,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>184°03'24.6"</t>
+          <t>207°10'03.3"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>72°15'24.7"</t>
+          <t>69°07'19.2"</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>262.4877771880527</v>
+        <v>143.388990578176</v>
       </c>
       <c r="E19" t="n">
-        <v>79.99319958693836</v>
+        <v>51.10087756085862</v>
       </c>
       <c r="F19" t="n">
-        <v>250.0018423791494</v>
+        <v>133.974262198149</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -5982,7 +7302,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>171°10'47.2"</t>
+          <t>151°14'49.0"</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -5990,36 +7310,36 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>10999.96215367557</v>
+        <v>1019.159914684784</v>
       </c>
       <c r="H20" t="n">
-        <v>7100.016961353121</v>
+        <v>1154.377632342006</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>→edge_K9_G</t>
+          <t>→edge_K9_K10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>171°10'47.2"</t>
+          <t>151°14'49.0"</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>63°26'12.0"</t>
+          <t>40°22'08.2"</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>223.6066970318541</v>
+        <v>163.7434618707985</v>
       </c>
       <c r="E21" t="n">
-        <v>99.99399857207619</v>
+        <v>124.7544302343493</v>
       </c>
       <c r="F21" t="n">
-        <v>200.0028879968063</v>
+        <v>106.0577835066174</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -6027,101 +7347,251 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>190°00'03.5"</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>11099.95615224765</v>
+        <v>1143.914344919134</v>
       </c>
       <c r="H22" t="n">
-        <v>7300.019849349927</v>
+        <v>1260.435415848624</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>→edge_G_G2</t>
+          <t>→edge_K10_K11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>180°00'01.0"</t>
+          <t>190°00'03.5"</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>63°26'12.9"</t>
-        </is>
+          <t>50°22'11.7"</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>135.1748654285916</v>
+      </c>
+      <c r="E23" t="n">
+        <v>86.21839255519777</v>
+      </c>
+      <c r="F23" t="n">
+        <v>104.1087557741215</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
     </row>
-    <row r="24"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>152°59'35.5"</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>1230.132737474331</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1364.544171622745</v>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>闭合差项</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>→edge_K11_K12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>152°59'35.5"</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23°21'47.1"</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>195.8868156270867</v>
+      </c>
+      <c r="E25" t="n">
+        <v>179.8261045269858</v>
+      </c>
+      <c r="F25" t="n">
+        <v>77.68022056591911</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>方位角闭合差(")</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>7.133233264808969</v>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>212°17'06.0"</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>1409.958842001317</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1442.224392188664</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f_x(m)</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>-0.04384775235121197</v>
-      </c>
+          <t>→edge_K12_G</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>212°17'06.0"</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>55°38'53.2"</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>196.5510278543762</v>
+      </c>
+      <c r="E27" t="n">
+        <v>110.9086578487502</v>
+      </c>
+      <c r="F27" t="n">
+        <v>162.2700716854486</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f_y(m)</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0.01984934992651688</v>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>1520.867499850067</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1604.494463874113</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>→edge_G_G2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>197°25'08.5"</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>73°04'01.7"</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>闭合差项</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>方位角闭合差(")</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-3.616237120651302</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>f_x(m)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.02539985006728784</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>f_y(m)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.02283612588712458</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>f_D(m)</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>0.04813130040585367</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="B35" t="n">
+        <v>0.03415612725373449</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>全长(m)</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>2562.006884933738</v>
+      <c r="B36" t="n">
+        <v>2019.479207583565</v>
       </c>
     </row>
   </sheetData>

--- a/output/一级导线观测手簿.xlsx
+++ b/output/一级导线观测手簿.xlsx
@@ -426,10 +426,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -590,16 +590,52 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>方位基准</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B2→B (起始), G→G2 (终止)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>起始方位角</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B2→B = 69°29'39.5"</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>终止方位角</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>G→G2 = 73°04'05.3"</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>教学声明</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>本数据基于RTK坐标模拟生成, 仅供教学使用, 非真实外业观测数据
 目标等级: grade_1
@@ -705,16 +741,8 @@
           <t>2.44</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>359°59'58.8"</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -745,16 +773,8 @@
           <t>2.44</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>359°59'58.8"</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -787,14 +807,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>168°21'44.5"</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>168°21'45.7"</t>
-        </is>
-      </c>
+          <t>168°21'45.1"</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -827,7 +843,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>168°21'44.5"</t>
+          <t>168°21'46.3"</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,16 +881,8 @@
           <t>0.83</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>359°59'59.6"</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -905,16 +913,8 @@
           <t>0.83</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>359°59'59.6"</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -947,14 +947,10 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>348°21'48.5"</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>348°21'48.9"</t>
-        </is>
-      </c>
+          <t>168°21'48.7"</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -987,12 +983,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>348°21'48.5"</t>
+          <t>168°21'49.1"</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>348°21'48.9"</t>
+          <t>168°21'48.9"</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1021,8 @@
           <t>-0.51</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0°00'00.3"</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1065,16 +1053,8 @@
           <t>-0.51</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0°00'00.3"</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1107,14 +1087,10 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>165°41'16.2"</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>165°41'16.0"</t>
-        </is>
-      </c>
+          <t>165°41'16.8"</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1147,7 +1123,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>165°41'16.2"</t>
+          <t>165°41'15.2"</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1185,16 +1161,8 @@
           <t>1.52</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>359°59'59.2"</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1225,16 +1193,8 @@
           <t>1.52</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>359°59'59.2"</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1267,14 +1227,10 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>345°41'17.2"</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>345°41'17.9"</t>
-        </is>
-      </c>
+          <t>165°41'17.3"</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1307,12 +1263,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>345°41'17.2"</t>
+          <t>165°41'18.6"</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>345°41'17.9"</t>
+          <t>165°41'17.9"</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1301,8 @@
           <t>-0.76</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0°00'00.4"</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1385,16 +1333,8 @@
           <t>-0.76</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0°00'00.4"</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1427,14 +1367,10 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>24°35'18.2"</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>24°35'17.8"</t>
-        </is>
-      </c>
+          <t>204°35'17.4"</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1467,12 +1403,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>24°35'18.2"</t>
+          <t>204°35'18.2"</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24°35'17.8"</t>
+          <t>204°35'17.8"</t>
         </is>
       </c>
     </row>
@@ -1505,16 +1441,8 @@
           <t>1.26</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>359°59'59.4"</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1545,16 +1473,8 @@
           <t>1.26</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>359°59'59.4"</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1587,14 +1507,10 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>24°35'22.4"</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>24°35'23.0"</t>
-        </is>
-      </c>
+          <t>204°35'22.3"</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1627,12 +1543,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24°35'22.4"</t>
+          <t>204°35'23.7"</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24°35'23.0"</t>
+          <t>204°35'23.0"</t>
         </is>
       </c>
     </row>
@@ -1665,16 +1581,8 @@
           <t>-0.32</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0°00'00.2"</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1705,16 +1613,8 @@
           <t>-0.32</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0°00'00.2"</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1747,14 +1647,10 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>136°00'16.8"</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>136°00'16.6"</t>
-        </is>
-      </c>
+          <t>136°00'17.6"</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1787,7 +1683,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>136°00'16.8"</t>
+          <t>136°00'15.6"</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1825,16 +1721,8 @@
           <t>0.30</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>359°59'59.9"</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1865,16 +1753,8 @@
           <t>0.30</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>359°59'59.9"</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1907,14 +1787,10 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>316°00'11.4"</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>316°00'11.5"</t>
-        </is>
-      </c>
+          <t>136°00'12.4"</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1947,12 +1823,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>316°00'11.4"</t>
+          <t>136°00'10.6"</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>316°00'11.5"</t>
+          <t>136°00'11.5"</t>
         </is>
       </c>
     </row>
@@ -1985,16 +1861,8 @@
           <t>-0.25</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0°00'00.1"</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2025,16 +1893,8 @@
           <t>-0.25</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0°00'00.1"</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2067,14 +1927,10 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>177°58'47.6"</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>177°58'47.5"</t>
-        </is>
-      </c>
+          <t>177°58'47.7"</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2107,7 +1963,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>177°58'47.6"</t>
+          <t>177°58'47.2"</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2145,16 +2001,8 @@
           <t>-2.33</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0°00'01.2"</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2185,16 +2033,8 @@
           <t>-2.33</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>0°00'01.2"</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2227,14 +2067,10 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>357°58'48.6"</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>357°58'47.4"</t>
-        </is>
-      </c>
+          <t>177°58'49.6"</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2267,12 +2103,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>357°58'48.6"</t>
+          <t>177°58'45.3"</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>357°58'47.4"</t>
+          <t>177°58'47.4"</t>
         </is>
       </c>
     </row>
@@ -2305,16 +2141,8 @@
           <t>0.35</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>359°59'59.8"</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2345,16 +2173,8 @@
           <t>0.35</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>359°59'59.8"</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2387,14 +2207,10 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8°23'23.3"</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>8°23'23.5"</t>
-        </is>
-      </c>
+          <t>188°23'22.5"</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2427,12 +2243,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8°23'23.3"</t>
+          <t>188°23'24.5"</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8°23'23.5"</t>
+          <t>188°23'23.5"</t>
         </is>
       </c>
     </row>
@@ -2465,16 +2281,8 @@
           <t>-1.76</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0°00'00.9"</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2505,16 +2313,8 @@
           <t>-1.76</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0°00'00.9"</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2547,14 +2347,10 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8°23'22.7"</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>8°23'21.8"</t>
-        </is>
-      </c>
+          <t>188°23'22.1"</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2587,12 +2383,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8°23'22.7"</t>
+          <t>188°23'21.6"</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8°23'21.8"</t>
+          <t>188°23'21.8"</t>
         </is>
       </c>
     </row>
@@ -2625,16 +2421,8 @@
           <t>0.87</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>359°59'59.6"</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2665,16 +2453,8 @@
           <t>0.87</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>359°59'59.6"</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2707,14 +2487,10 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>9°24'38.4"</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>9°24'38.8"</t>
-        </is>
-      </c>
+          <t>189°24'39.8"</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2747,12 +2523,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>9°24'38.4"</t>
+          <t>189°24'37.8"</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>9°24'38.8"</t>
+          <t>189°24'38.8"</t>
         </is>
       </c>
     </row>
@@ -2785,16 +2561,8 @@
           <t>-1.34</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>0°00'00.7"</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2825,16 +2593,8 @@
           <t>-1.34</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>0°00'00.7"</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2867,14 +2627,10 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9°24'36.1"</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>9°24'35.4"</t>
-        </is>
-      </c>
+          <t>189°24'35.2"</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2907,12 +2663,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>9°24'36.1"</t>
+          <t>189°24'35.6"</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9°24'35.4"</t>
+          <t>189°24'35.4"</t>
         </is>
       </c>
     </row>
@@ -2945,16 +2701,8 @@
           <t>-0.51</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>0°00'00.3"</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2985,16 +2733,8 @@
           <t>-0.51</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>0°00'00.3"</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3027,14 +2767,10 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2°02'12.9"</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>2°02'12.6"</t>
-        </is>
-      </c>
+          <t>182°02'12.9"</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3067,12 +2803,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2°02'12.9"</t>
+          <t>182°02'12.3"</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2°02'12.6"</t>
+          <t>182°02'12.6"</t>
         </is>
       </c>
     </row>
@@ -3105,16 +2841,8 @@
           <t>0.90</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>359°59'59.6"</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3145,16 +2873,8 @@
           <t>0.90</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>359°59'59.6"</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3187,14 +2907,10 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2°02'07.8"</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2°02'08.2"</t>
-        </is>
-      </c>
+          <t>182°02'08.1"</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3227,12 +2943,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2°02'07.8"</t>
+          <t>182°02'08.4"</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2°02'08.2"</t>
+          <t>182°02'08.2"</t>
         </is>
       </c>
     </row>
@@ -3265,16 +2981,8 @@
           <t>0.91</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>359°59'59.5"</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3305,16 +3013,8 @@
           <t>0.91</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>359°59'59.5"</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3347,14 +3047,10 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>27°10'00.9"</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>27°10'01.4"</t>
-        </is>
-      </c>
+          <t>207°10'00.7"</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3387,12 +3083,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>27°10'00.9"</t>
+          <t>207°10'02.0"</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>27°10'01.4"</t>
+          <t>207°10'01.4"</t>
         </is>
       </c>
     </row>
@@ -3425,16 +3121,8 @@
           <t>-0.11</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>0°00'00.1"</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3465,16 +3153,8 @@
           <t>-0.11</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>0°00'00.1"</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3507,14 +3187,10 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>27°10'05.3"</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>27°10'05.3"</t>
-        </is>
-      </c>
+          <t>207°10'06.3"</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3547,12 +3223,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>27°10'05.3"</t>
+          <t>207°10'04.2"</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>27°10'05.3"</t>
+          <t>207°10'05.3"</t>
         </is>
       </c>
     </row>
@@ -3585,16 +3261,8 @@
           <t>-0.04</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3625,16 +3293,8 @@
           <t>-0.04</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3670,11 +3330,7 @@
           <t>151°14'46.7"</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>151°14'46.7"</t>
-        </is>
-      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3745,16 +3401,8 @@
           <t>0.10</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>360°00'00.0"</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3785,16 +3433,8 @@
           <t>0.10</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>360°00'00.0"</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3827,14 +3467,10 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>331°14'51.2"</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>331°14'51.3"</t>
-        </is>
-      </c>
+          <t>151°14'52.2"</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3867,12 +3503,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>331°14'51.2"</t>
+          <t>151°14'50.4"</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>331°14'51.3"</t>
+          <t>151°14'51.3"</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3541,8 @@
           <t>-1.78</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>0°00'00.9"</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3945,16 +3573,8 @@
           <t>-1.78</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>0°00'00.9"</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3987,14 +3607,10 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>10°00'04.4"</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>10°00'03.5"</t>
-        </is>
-      </c>
+          <t>190°00'05.6"</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4027,12 +3643,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>10°00'04.4"</t>
+          <t>190°00'01.4"</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>10°00'03.5"</t>
+          <t>190°00'03.5"</t>
         </is>
       </c>
     </row>
@@ -4065,16 +3681,8 @@
           <t>0.24</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>359°59'59.9"</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4105,16 +3713,8 @@
           <t>0.24</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>359°59'59.9"</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4147,14 +3747,10 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>10°00'03.4"</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>10°00'03.5"</t>
-        </is>
-      </c>
+          <t>190°00'02.8"</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4187,12 +3783,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>10°00'03.4"</t>
+          <t>190°00'04.1"</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>10°00'03.5"</t>
+          <t>190°00'03.5"</t>
         </is>
       </c>
     </row>
@@ -4225,16 +3821,8 @@
           <t>-0.30</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>0°00'00.2"</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4265,16 +3853,8 @@
           <t>-0.30</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>0°00'00.2"</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4307,14 +3887,10 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>152°59'34.3"</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>152°59'34.1"</t>
-        </is>
-      </c>
+          <t>152°59'32.8"</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4347,7 +3923,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>152°59'34.3"</t>
+          <t>152°59'35.4"</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4385,16 +3961,8 @@
           <t>3.31</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>359°59'58.3"</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4425,16 +3993,8 @@
           <t>3.31</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>359°59'58.3"</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4467,14 +4027,10 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>332°59'35.2"</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>332°59'36.8"</t>
-        </is>
-      </c>
+          <t>152°59'36.1"</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4507,12 +4063,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>332°59'35.2"</t>
+          <t>152°59'37.6"</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>332°59'36.8"</t>
+          <t>152°59'36.8"</t>
         </is>
       </c>
     </row>
@@ -4545,16 +4101,8 @@
           <t>-4.09</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>0°00'02.0"</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4585,16 +4133,8 @@
           <t>-4.09</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>0°00'02.0"</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4627,14 +4167,10 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>32°17'08.3"</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>32°17'06.2"</t>
-        </is>
-      </c>
+          <t>212°17'07.8"</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4667,12 +4203,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>32°17'08.3"</t>
+          <t>212°17'04.7"</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>32°17'06.2"</t>
+          <t>212°17'06.2"</t>
         </is>
       </c>
     </row>
@@ -4705,16 +4241,8 @@
           <t>-0.38</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>0°00'00.2"</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4745,16 +4273,8 @@
           <t>-0.38</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>0°00'00.2"</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4787,14 +4307,10 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>32°17'06.0"</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>32°17'05.8"</t>
-        </is>
-      </c>
+          <t>212°17'05.9"</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4827,12 +4343,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>32°17'06.0"</t>
+          <t>212°17'05.7"</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>32°17'05.8"</t>
+          <t>212°17'05.8"</t>
         </is>
       </c>
     </row>
@@ -4865,16 +4381,8 @@
           <t>1.25</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>359°59'59.4"</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4905,16 +4413,8 @@
           <t>1.25</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>359°59'59.4"</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4947,14 +4447,10 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>17°25'08.8"</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>17°25'09.4"</t>
-        </is>
-      </c>
+          <t>197°25'09.5"</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4987,12 +4483,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>17°25'08.8"</t>
+          <t>197°25'09.4"</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>17°25'09.4"</t>
+          <t>197°25'09.4"</t>
         </is>
       </c>
     </row>
@@ -5025,16 +4521,8 @@
           <t>-1.47</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>0°00'00.7"</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5065,16 +4553,8 @@
           <t>-1.47</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>0°00'00.7"</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>0°00'00.0"</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5107,14 +4587,10 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>17°25'08.3"</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>17°25'07.6"</t>
-        </is>
-      </c>
+          <t>197°25'08.0"</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5147,12 +4623,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>17°25'08.3"</t>
+          <t>197°25'07.2"</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17°25'07.6"</t>
+          <t>197°25'07.6"</t>
         </is>
       </c>
     </row>

--- a/output/一级导线观测手簿.xlsx
+++ b/output/一级导线观测手簿.xlsx
@@ -639,7 +639,6 @@
         <is>
           <t>本数据基于RTK坐标模拟生成, 仅供教学使用, 非真实外业观测数据
 目标等级: grade_1
-导线角度扰动 σ = 0.5"
 导线距离扰动 σ = 0.5 mm
 随机种子: 20260616
 本数据基于数学真值假设模拟生成, 不代表RTK实测精度可达目标等级</t>
@@ -733,12 +732,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0°02'30.1"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -765,12 +764,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>180°02'28.6"</t>
+          <t>179°59'57.6"</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -797,17 +796,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>168°24'20.4"</t>
+          <t>168°21'45.1"</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>168°21'50.2"</t>
+          <t>168°21'45.1"</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -833,22 +832,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>348°24'19.5"</t>
+          <t>348°21'43.9"</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>168°21'51.0"</t>
+          <t>168°21'46.3"</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>168°21'50.6"</t>
+          <t>168°21'45.7"</t>
         </is>
       </c>
     </row>
@@ -873,12 +872,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>90°02'29.5"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -905,12 +904,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>270°02'27.7"</t>
+          <t>269°59'59.2"</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -937,12 +936,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>258°24'18.2"</t>
+          <t>258°21'48.7"</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -973,22 +972,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78°24'18.6"</t>
+          <t>78°21'48.3"</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>168°21'50.9"</t>
+          <t>168°21'49.1"</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>168°21'49.8"</t>
+          <t>168°21'48.9"</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1012,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0°02'29.8"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1045,12 +1044,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>180°02'28.8"</t>
+          <t>180°00'00.5"</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1077,17 +1076,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>165°43'46.0"</t>
+          <t>165°41'16.8"</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>165°41'16.2"</t>
+          <t>165°41'16.8"</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1113,22 +1112,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>345°43'45.7"</t>
+          <t>345°41'15.7"</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>165°41'16.9"</t>
+          <t>165°41'15.2"</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>165°41'16.5"</t>
+          <t>165°41'16.0"</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1152,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>90°02'30.5"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1185,12 +1184,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>270°02'31.4"</t>
+          <t>269°59'58.5"</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1217,17 +1216,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>255°43'47.0"</t>
+          <t>255°41'17.3"</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>165°41'16.5"</t>
+          <t>165°41'17.3"</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1253,22 +1252,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75°43'47.8"</t>
+          <t>75°41'17.1"</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>165°41'16.4"</t>
+          <t>165°41'18.6"</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>165°41'16.5"</t>
+          <t>165°41'17.9"</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1292,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0°02'29.5"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1325,12 +1324,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>180°02'28.2"</t>
+          <t>180°00'00.8"</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1357,17 +1356,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>204°37'51.7"</t>
+          <t>204°35'17.4"</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>204°35'22.3"</t>
+          <t>204°35'17.4"</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1393,22 +1392,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>24°37'51.9"</t>
+          <t>24°35'18.9"</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>204°35'23.7"</t>
+          <t>204°35'18.2"</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>204°35'23.0"</t>
+          <t>204°35'17.8"</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1432,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>90°02'31.0"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1465,12 +1464,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>270°02'29.3"</t>
+          <t>269°59'58.7"</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1497,17 +1496,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>294°37'49.5"</t>
+          <t>294°35'22.3"</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>204°35'18.5"</t>
+          <t>204°35'22.3"</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1533,22 +1532,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>114°37'50.5"</t>
+          <t>114°35'22.5"</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>204°35'21.1"</t>
+          <t>204°35'23.7"</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>204°35'19.8"</t>
+          <t>204°35'23.0"</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1572,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0°02'30.1"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1605,12 +1604,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>180°02'30.3"</t>
+          <t>180°00'00.3"</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1637,17 +1636,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>136°02'45.5"</t>
+          <t>136°00'17.6"</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>136°00'15.4"</t>
+          <t>136°00'17.6"</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1673,22 +1672,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>316°02'45.7"</t>
+          <t>316°00'15.9"</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>136°00'15.4"</t>
+          <t>136°00'15.6"</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>136°00'15.4"</t>
+          <t>136°00'16.6"</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1712,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>90°02'30.1"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1745,12 +1744,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>270°02'32.4"</t>
+          <t>269°59'59.7"</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1777,17 +1776,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>226°02'44.4"</t>
+          <t>226°00'12.4"</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>136°00'14.3"</t>
+          <t>136°00'12.4"</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1813,22 +1812,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>46°02'42.5"</t>
+          <t>46°00'10.3"</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>136°00'10.1"</t>
+          <t>136°00'10.6"</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>136°00'12.2"</t>
+          <t>136°00'11.5"</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1852,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0°02'29.4"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1885,12 +1884,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>180°02'31.0"</t>
+          <t>180°00'00.3"</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1917,17 +1916,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>178°01'16.8"</t>
+          <t>177°58'47.7"</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>177°58'47.3"</t>
+          <t>177°58'47.7"</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1953,17 +1952,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>358°01'18.8"</t>
+          <t>357°58'47.5"</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>177°58'47.7"</t>
+          <t>177°58'47.2"</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1993,12 +1992,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>90°02'29.4"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2025,12 +2024,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>270°02'28.7"</t>
+          <t>270°00'02.3"</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2057,17 +2056,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>268°01'15.9"</t>
+          <t>267°58'49.6"</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>177°58'46.6"</t>
+          <t>177°58'49.6"</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2093,22 +2092,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>88°01'15.1"</t>
+          <t>87°58'47.6"</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>177°58'46.4"</t>
+          <t>177°58'45.3"</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>177°58'46.5"</t>
+          <t>177°58'47.4"</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2132,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0°02'30.9"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2165,12 +2164,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>180°02'32.3"</t>
+          <t>179°59'59.7"</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2197,17 +2196,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>188°25'54.1"</t>
+          <t>188°23'22.5"</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>188°23'23.2"</t>
+          <t>188°23'22.5"</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2233,22 +2232,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8°25'55.8"</t>
+          <t>8°23'24.1"</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>188°23'24.5"</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>188°23'23.5"</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>188°23'23.3"</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2272,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>90°02'30.0"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2305,12 +2304,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>270°02'29.9"</t>
+          <t>270°00'01.8"</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2337,17 +2336,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>278°25'52.8"</t>
+          <t>278°23'22.1"</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>188°23'22.8"</t>
+          <t>188°23'22.1"</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2373,22 +2372,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>98°25'56.6"</t>
+          <t>98°23'23.4"</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>188°23'26.7"</t>
+          <t>188°23'21.6"</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>188°23'24.8"</t>
+          <t>188°23'21.8"</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2412,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0°02'30.3"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2445,12 +2444,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>180°02'32.9"</t>
+          <t>179°59'59.1"</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2477,17 +2476,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>189°27'09.0"</t>
+          <t>189°24'39.8"</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>189°24'38.8"</t>
+          <t>189°24'39.8"</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2513,22 +2512,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>9°27'08.1"</t>
+          <t>9°24'36.9"</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>189°24'35.2"</t>
+          <t>189°24'37.8"</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>189°24'37.0"</t>
+          <t>189°24'38.8"</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2552,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>90°02'29.8"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -2585,12 +2584,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>270°02'29.9"</t>
+          <t>270°00'01.3"</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -2617,17 +2616,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>279°27'09.2"</t>
+          <t>279°24'35.2"</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>189°24'39.4"</t>
+          <t>189°24'35.2"</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -2653,22 +2652,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>99°27'07.2"</t>
+          <t>99°24'36.9"</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>189°24'37.2"</t>
+          <t>189°24'35.6"</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>189°24'38.3"</t>
+          <t>189°24'35.4"</t>
         </is>
       </c>
     </row>
@@ -2693,12 +2692,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0°02'29.3"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2725,12 +2724,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>180°02'29.4"</t>
+          <t>180°00'00.5"</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -2757,17 +2756,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>182°04'42.7"</t>
+          <t>182°02'12.9"</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>182°02'13.5"</t>
+          <t>182°02'12.9"</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2793,22 +2792,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2°04'41.4"</t>
+          <t>2°02'12.8"</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>182°02'12.1"</t>
+          <t>182°02'12.3"</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>182°02'12.8"</t>
+          <t>182°02'12.6"</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2832,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>90°02'30.0"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -2865,12 +2864,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>270°02'28.3"</t>
+          <t>269°59'59.1"</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -2897,17 +2896,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>272°04'44.5"</t>
+          <t>272°02'08.1"</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>182°02'14.5"</t>
+          <t>182°02'08.1"</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -2933,22 +2932,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>92°04'46.3"</t>
+          <t>92°02'07.5"</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>182°02'18.0"</t>
+          <t>182°02'08.4"</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>182°02'16.3"</t>
+          <t>182°02'08.2"</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2972,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0°02'30.8"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3005,12 +3004,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>180°02'30.5"</t>
+          <t>179°59'59.1"</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3037,17 +3036,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>207°12'35.8"</t>
+          <t>207°10'00.7"</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>207°10'05.1"</t>
+          <t>207°10'00.7"</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3073,22 +3072,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>27°12'36.9"</t>
+          <t>27°10'01.1"</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>207°10'06.4"</t>
+          <t>207°10'02.0"</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>207°10'05.7"</t>
+          <t>207°10'01.4"</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3112,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>90°02'30.0"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3145,12 +3144,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>270°02'33.0"</t>
+          <t>270°00'00.1"</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3177,17 +3176,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>297°12'34.5"</t>
+          <t>297°10'06.3"</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>207°10'04.5"</t>
+          <t>207°10'06.3"</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -3213,22 +3212,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>117°12'33.6"</t>
+          <t>117°10'04.3"</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>207°10'00.6"</t>
+          <t>207°10'04.2"</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>207°10'02.6"</t>
+          <t>207°10'05.3"</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3252,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0°02'31.1"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -3285,12 +3284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>180°02'30.2"</t>
+          <t>180°00'00.0"</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -3317,17 +3316,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>151°17'20.9"</t>
+          <t>151°14'46.7"</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>151°14'49.8"</t>
+          <t>151°14'46.7"</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -3353,22 +3352,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>331°17'25.0"</t>
+          <t>331°14'46.8"</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>151°14'54.8"</t>
+          <t>151°14'46.7"</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>151°14'52.3"</t>
+          <t>151°14'46.7"</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3392,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>90°02'29.7"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -3425,12 +3424,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>270°02'30.0"</t>
+          <t>269°59'59.9"</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -3457,17 +3456,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>241°17'17.9"</t>
+          <t>241°14'52.2"</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>151°14'48.3"</t>
+          <t>151°14'52.2"</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -3493,22 +3492,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>61°17'18.1"</t>
+          <t>61°14'50.3"</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>151°14'48.0"</t>
+          <t>151°14'50.4"</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>151°14'48.2"</t>
+          <t>151°14'51.3"</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3532,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0°02'28.7"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -3565,12 +3564,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>180°02'27.5"</t>
+          <t>180°00'01.8"</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -3597,17 +3596,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>190°02'33.7"</t>
+          <t>190°00'05.6"</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>190°00'05.0"</t>
+          <t>190°00'05.6"</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -3633,22 +3632,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>10°02'34.5"</t>
+          <t>10°00'03.2"</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>190°00'07.0"</t>
+          <t>190°00'01.4"</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>190°00'06.0"</t>
+          <t>190°00'03.5"</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3672,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>90°02'30.2"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -3705,12 +3704,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>270°02'28.6"</t>
+          <t>269°59'59.8"</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -3737,17 +3736,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>280°02'33.6"</t>
+          <t>280°00'02.8"</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>190°00'03.4"</t>
+          <t>190°00'02.8"</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -3773,22 +3772,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>100°02'32.4"</t>
+          <t>100°00'03.9"</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>190°00'03.8"</t>
+          <t>190°00'04.1"</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>190°00'03.6"</t>
+          <t>190°00'03.5"</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3812,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0°02'30.4"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -3845,12 +3844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>180°02'31.9"</t>
+          <t>180°00'00.3"</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -3877,17 +3876,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>153°02'05.7"</t>
+          <t>152°59'32.8"</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>152°59'35.3"</t>
+          <t>152°59'32.8"</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -3913,22 +3912,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>333°02'06.4"</t>
+          <t>332°59'35.7"</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>152°59'34.5"</t>
+          <t>152°59'35.4"</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>152°59'34.9"</t>
+          <t>152°59'34.1"</t>
         </is>
       </c>
     </row>
@@ -3953,12 +3952,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>90°02'30.0"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -3985,12 +3984,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>270°02'29.5"</t>
+          <t>269°59'56.7"</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -4017,17 +4016,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>243°02'03.2"</t>
+          <t>242°59'36.1"</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>152°59'33.2"</t>
+          <t>152°59'36.1"</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4053,22 +4052,22 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>63°02'05.3"</t>
+          <t>62°59'34.3"</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>152°59'35.8"</t>
+          <t>152°59'37.6"</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>152°59'34.5"</t>
+          <t>152°59'36.8"</t>
         </is>
       </c>
     </row>
@@ -4093,12 +4092,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0°02'29.7"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -4125,12 +4124,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>180°02'28.3"</t>
+          <t>180°00'04.1"</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -4157,17 +4156,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>212°19'35.9"</t>
+          <t>212°17'07.8"</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>212°17'06.2"</t>
+          <t>212°17'07.8"</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -4193,22 +4192,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>32°19'35.0"</t>
+          <t>32°17'08.7"</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>212°17'06.7"</t>
+          <t>212°17'04.7"</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>212°17'06.4"</t>
+          <t>212°17'06.2"</t>
         </is>
       </c>
     </row>
@@ -4233,12 +4232,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>90°02'30.0"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -4265,12 +4264,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>270°02'30.4"</t>
+          <t>270°00'00.4"</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -4297,17 +4296,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>302°19'35.4"</t>
+          <t>302°17'05.9"</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>212°17'05.4"</t>
+          <t>212°17'05.9"</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -4333,22 +4332,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>122°19'34.8"</t>
+          <t>122°17'06.0"</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>212°17'04.4"</t>
+          <t>212°17'05.7"</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>212°17'04.9"</t>
+          <t>212°17'05.8"</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4372,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0°02'29.4"</t>
+          <t>0°00'00.0"</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -4405,12 +4404,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>180°02'29.0"</t>
+          <t>179°59'58.7"</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -4437,17 +4436,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>197°27'35.6"</t>
+          <t>197°25'09.5"</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>197°25'06.2"</t>
+          <t>197°25'09.5"</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -4473,22 +4472,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>17°27'36.5"</t>
+          <t>17°25'08.2"</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>197°25'07.5"</t>
+          <t>197°25'09.4"</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>197°25'06.9"</t>
+          <t>197°25'09.4"</t>
         </is>
       </c>
     </row>
@@ -4513,12 +4512,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>90°02'29.4"</t>
+          <t>90°00'00.0"</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -4545,12 +4544,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>270°02'27.0"</t>
+          <t>270°00'01.5"</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -4577,17 +4576,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>287°27'38.1"</t>
+          <t>287°25'08.0"</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>197°25'08.7"</t>
+          <t>197°25'08.0"</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -4613,22 +4612,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>107°27'37.3"</t>
+          <t>107°25'08.6"</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>197°25'10.3"</t>
+          <t>197°25'07.2"</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>197°25'09.5"</t>
+          <t>197°25'07.6"</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4650,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
@@ -4710,22 +4709,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>171.3294034362016</v>
+        <v>171.3296782147522</v>
       </c>
       <c r="D2" t="n">
-        <v>171.3320389369026</v>
+        <v>171.3297813283291</v>
       </c>
       <c r="E2" t="n">
-        <v>171.3297022469407</v>
+        <v>171.3299924507707</v>
       </c>
       <c r="F2" t="n">
-        <v>2.635500700989724</v>
+        <v>0.3142360185393045</v>
       </c>
       <c r="G2" t="n">
-        <v>171.330381540015</v>
+        <v>171.329817331284</v>
       </c>
       <c r="H2" t="n">
-        <v>171.329761760525</v>
+        <v>171.3294933455056</v>
       </c>
     </row>
     <row r="3">
@@ -4740,22 +4739,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>171.3302445775376</v>
+        <v>171.3279221212715</v>
       </c>
       <c r="D3" t="n">
-        <v>171.3309927197661</v>
+        <v>171.3290424872574</v>
       </c>
       <c r="E3" t="n">
-        <v>171.3293246342422</v>
+        <v>171.3287467398517</v>
       </c>
       <c r="F3" t="n">
-        <v>1.668085523931495</v>
+        <v>1.120365985968874</v>
       </c>
       <c r="G3" t="n">
-        <v>171.3301873105153</v>
+        <v>171.3285704494602</v>
       </c>
       <c r="H3" t="n">
-        <v>171.329761760525</v>
+        <v>171.3294933455056</v>
       </c>
     </row>
     <row r="4">
@@ -4770,22 +4769,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>171.3277879593139</v>
+        <v>171.3307379909682</v>
       </c>
       <c r="D4" t="n">
-        <v>171.3300796494161</v>
+        <v>171.330334946902</v>
       </c>
       <c r="E4" t="n">
-        <v>171.3275151266562</v>
+        <v>171.3298154925244</v>
       </c>
       <c r="F4" t="n">
-        <v>2.564522759854526</v>
+        <v>0.9224984437992134</v>
       </c>
       <c r="G4" t="n">
-        <v>171.3284609117954</v>
+        <v>171.3302961434648</v>
       </c>
       <c r="H4" t="n">
-        <v>171.329761760525</v>
+        <v>171.3294933455056</v>
       </c>
     </row>
     <row r="5">
@@ -4800,22 +4799,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>171.3287224693375</v>
+        <v>171.3283607326331</v>
       </c>
       <c r="D5" t="n">
-        <v>171.3310193306617</v>
+        <v>171.3293512718502</v>
       </c>
       <c r="E5" t="n">
-        <v>171.3303100393235</v>
+        <v>171.3301563689574</v>
       </c>
       <c r="F5" t="n">
-        <v>2.296861324140309</v>
+        <v>1.795636324288807</v>
       </c>
       <c r="G5" t="n">
-        <v>171.3300172797742</v>
+        <v>171.3292894578136</v>
       </c>
       <c r="H5" t="n">
-        <v>171.329761760525</v>
+        <v>171.3294933455056</v>
       </c>
     </row>
     <row r="6">
@@ -4830,22 +4829,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>125.0651239705007</v>
+        <v>125.0653919722548</v>
       </c>
       <c r="D6" t="n">
-        <v>125.0632118410759</v>
+        <v>125.0651146203921</v>
       </c>
       <c r="E6" t="n">
-        <v>125.0633692597232</v>
+        <v>125.0661986906014</v>
       </c>
       <c r="F6" t="n">
-        <v>1.91212942480945</v>
+        <v>1.084070209287802</v>
       </c>
       <c r="G6" t="n">
-        <v>125.0639016904333</v>
+        <v>125.0655684277494</v>
       </c>
       <c r="H6" t="n">
-        <v>125.0647150134671</v>
+        <v>125.0649859305766</v>
       </c>
     </row>
     <row r="7">
@@ -4860,22 +4859,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>125.0634119951376</v>
+        <v>125.0656103669958</v>
       </c>
       <c r="D7" t="n">
-        <v>125.0669367120031</v>
+        <v>125.0639023824566</v>
       </c>
       <c r="E7" t="n">
-        <v>125.0646568090678</v>
+        <v>125.0645498566374</v>
       </c>
       <c r="F7" t="n">
-        <v>3.524716865484834</v>
+        <v>1.707984539109475</v>
       </c>
       <c r="G7" t="n">
-        <v>125.0650018387361</v>
+        <v>125.0646875353633</v>
       </c>
       <c r="H7" t="n">
-        <v>125.0647150134671</v>
+        <v>125.0649859305766</v>
       </c>
     </row>
     <row r="8">
@@ -4890,22 +4889,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>125.0625692145721</v>
+        <v>125.0664286329718</v>
       </c>
       <c r="D8" t="n">
-        <v>125.065127866053</v>
+        <v>125.064634174296</v>
       </c>
       <c r="E8" t="n">
-        <v>125.0663863094111</v>
+        <v>125.0635305964784</v>
       </c>
       <c r="F8" t="n">
-        <v>3.817094838993285</v>
+        <v>2.898036493377276</v>
       </c>
       <c r="G8" t="n">
-        <v>125.0646944633454</v>
+        <v>125.0648644679154</v>
       </c>
       <c r="H8" t="n">
-        <v>125.0647150134671</v>
+        <v>125.0649859305766</v>
       </c>
     </row>
     <row r="9">
@@ -4920,22 +4919,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>125.065967950356</v>
+        <v>125.0649902913926</v>
       </c>
       <c r="D9" t="n">
-        <v>125.065482381186</v>
+        <v>125.0652521435791</v>
       </c>
       <c r="E9" t="n">
-        <v>125.0643358525191</v>
+        <v>125.0642274388634</v>
       </c>
       <c r="F9" t="n">
-        <v>1.632097836917978</v>
+        <v>1.024704715675284</v>
       </c>
       <c r="G9" t="n">
-        <v>125.0652620613537</v>
+        <v>125.0648232912784</v>
       </c>
       <c r="H9" t="n">
-        <v>125.0647150134671</v>
+        <v>125.0649859305766</v>
       </c>
     </row>
     <row r="10">
@@ -4950,22 +4949,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>134.9529916757516</v>
+        <v>134.9502450915442</v>
       </c>
       <c r="D10" t="n">
-        <v>134.9517608814345</v>
+        <v>134.9526228034941</v>
       </c>
       <c r="E10" t="n">
-        <v>134.9532259722673</v>
+        <v>134.953513201598</v>
       </c>
       <c r="F10" t="n">
-        <v>1.465090832766691</v>
+        <v>3.268110053767259</v>
       </c>
       <c r="G10" t="n">
-        <v>134.9526595098178</v>
+        <v>134.9521270322121</v>
       </c>
       <c r="H10" t="n">
-        <v>134.9521831598236</v>
+        <v>134.9520033228584</v>
       </c>
     </row>
     <row r="11">
@@ -4980,22 +4979,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>134.9521992970485</v>
+        <v>134.9522326961983</v>
       </c>
       <c r="D11" t="n">
-        <v>134.9519715514142</v>
+        <v>134.9513849263448</v>
       </c>
       <c r="E11" t="n">
-        <v>134.9525834237296</v>
+        <v>134.9540204270458</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6118723154031613</v>
+        <v>2.635500700989724</v>
       </c>
       <c r="G11" t="n">
-        <v>134.9522514240641</v>
+        <v>134.9525460165296</v>
       </c>
       <c r="H11" t="n">
-        <v>134.9521831598236</v>
+        <v>134.9520033228584</v>
       </c>
     </row>
     <row r="12">
@@ -5010,22 +5009,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>134.9505461685612</v>
+        <v>134.951683737084</v>
       </c>
       <c r="D12" t="n">
-        <v>134.9505268788475</v>
+        <v>134.9522260676808</v>
       </c>
       <c r="E12" t="n">
-        <v>134.9529401165389</v>
+        <v>134.9529742099093</v>
       </c>
       <c r="F12" t="n">
-        <v>2.413237691342829</v>
+        <v>1.290472825388633</v>
       </c>
       <c r="G12" t="n">
-        <v>134.9513377213159</v>
+        <v>134.9522946715581</v>
       </c>
       <c r="H12" t="n">
-        <v>134.9521831598236</v>
+        <v>134.9520033228584</v>
       </c>
     </row>
     <row r="13">
@@ -5040,22 +5039,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>134.952088323704</v>
+        <v>134.9513061243854</v>
       </c>
       <c r="D13" t="n">
-        <v>134.9529240286371</v>
+        <v>134.9497694494572</v>
       </c>
       <c r="E13" t="n">
-        <v>134.9524395999478</v>
+        <v>134.9520611395593</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8357049331095823</v>
+        <v>2.291690102168786</v>
       </c>
       <c r="G13" t="n">
-        <v>134.9524839840963</v>
+        <v>134.951045571134</v>
       </c>
       <c r="H13" t="n">
-        <v>134.9521831598236</v>
+        <v>134.9520033228584</v>
       </c>
     </row>
     <row r="14">
@@ -5070,22 +5069,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>149.5859756795022</v>
+        <v>149.5835102349138</v>
       </c>
       <c r="D14" t="n">
-        <v>149.5854182186113</v>
+        <v>149.5847175775951</v>
       </c>
       <c r="E14" t="n">
-        <v>149.5834197166409</v>
+        <v>149.5870144389192</v>
       </c>
       <c r="F14" t="n">
-        <v>2.555962861208627</v>
+        <v>3.504204005423617</v>
       </c>
       <c r="G14" t="n">
-        <v>149.5849378715848</v>
+        <v>149.585080750476</v>
       </c>
       <c r="H14" t="n">
-        <v>149.5849427858228</v>
+        <v>149.5850999747892</v>
       </c>
     </row>
     <row r="15">
@@ -5100,22 +5099,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>149.5851797903773</v>
+        <v>149.586305147581</v>
       </c>
       <c r="D15" t="n">
-        <v>149.5841338665925</v>
+        <v>149.5857795492917</v>
       </c>
       <c r="E15" t="n">
-        <v>149.5840470419024</v>
+        <v>149.5838674198668</v>
       </c>
       <c r="F15" t="n">
-        <v>1.132748474901746</v>
+        <v>2.437727714180937</v>
       </c>
       <c r="G15" t="n">
-        <v>149.5844535662908</v>
+        <v>149.5853173722465</v>
       </c>
       <c r="H15" t="n">
-        <v>149.5849427858228</v>
+        <v>149.5850999747892</v>
       </c>
     </row>
     <row r="16">
@@ -5130,22 +5129,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>149.5857547227733</v>
+        <v>149.5840248385142</v>
       </c>
       <c r="D16" t="n">
-        <v>149.5846490304403</v>
+        <v>149.5840675739286</v>
       </c>
       <c r="E16" t="n">
-        <v>149.5854400579184</v>
+        <v>149.587592290794</v>
       </c>
       <c r="F16" t="n">
-        <v>1.105692332998842</v>
+        <v>3.567452279867211</v>
       </c>
       <c r="G16" t="n">
-        <v>149.5852812703774</v>
+        <v>149.5852282344123</v>
       </c>
       <c r="H16" t="n">
-        <v>149.5849427858228</v>
+        <v>149.5850999747892</v>
       </c>
     </row>
     <row r="17">
@@ -5160,22 +5159,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>149.5856203655791</v>
+        <v>149.5853123878587</v>
       </c>
       <c r="D17" t="n">
-        <v>149.5855188481407</v>
+        <v>149.5832247933631</v>
       </c>
       <c r="E17" t="n">
-        <v>149.5841560913946</v>
+        <v>149.5857834448439</v>
       </c>
       <c r="F17" t="n">
-        <v>1.46427418451367</v>
+        <v>2.558651480853769</v>
       </c>
       <c r="G17" t="n">
-        <v>149.5850984350381</v>
+        <v>149.5847735420219</v>
       </c>
       <c r="H17" t="n">
-        <v>149.5849427858228</v>
+        <v>149.5850999747892</v>
       </c>
     </row>
     <row r="18">
@@ -5190,22 +5189,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>158.9500611591511</v>
+        <v>158.9520222559333</v>
       </c>
       <c r="D18" t="n">
-        <v>158.9506191271481</v>
+        <v>158.9516038968782</v>
       </c>
       <c r="E18" t="n">
-        <v>158.9499391354988</v>
+        <v>158.9511183277082</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6799916493207547</v>
+        <v>0.9039282250853375</v>
       </c>
       <c r="G18" t="n">
-        <v>158.9502064739327</v>
+        <v>158.9515814935066</v>
       </c>
       <c r="H18" t="n">
-        <v>158.9503626922977</v>
+        <v>158.9510395012817</v>
       </c>
     </row>
     <row r="19">
@@ -5220,22 +5219,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>158.9501692598077</v>
+        <v>158.9499717990413</v>
       </c>
       <c r="D19" t="n">
-        <v>158.9497979391961</v>
+        <v>158.9519856615972</v>
       </c>
       <c r="E19" t="n">
-        <v>158.9494433351975</v>
+        <v>158.9507548672801</v>
       </c>
       <c r="F19" t="n">
-        <v>0.725924610179618</v>
+        <v>2.013862555912738</v>
       </c>
       <c r="G19" t="n">
-        <v>158.9498035114004</v>
+        <v>158.9509041093062</v>
       </c>
       <c r="H19" t="n">
-        <v>158.9503626922977</v>
+        <v>158.9510395012817</v>
       </c>
     </row>
     <row r="20">
@@ -5250,22 +5249,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>158.9523397595241</v>
+        <v>158.9522199581128</v>
       </c>
       <c r="D20" t="n">
-        <v>158.947310333885</v>
+        <v>158.951193282894</v>
       </c>
       <c r="E20" t="n">
-        <v>158.949146993635</v>
+        <v>158.9509655372598</v>
       </c>
       <c r="F20" t="n">
-        <v>5.029425639037299</v>
+        <v>1.254420853058491</v>
       </c>
       <c r="G20" t="n">
-        <v>158.9495990290147</v>
+        <v>158.9514595927556</v>
       </c>
       <c r="H20" t="n">
-        <v>158.9503626922977</v>
+        <v>158.9510395012817</v>
       </c>
     </row>
     <row r="21">
@@ -5280,22 +5279,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>158.9527225385959</v>
+        <v>158.9515774095752</v>
       </c>
       <c r="D21" t="n">
-        <v>158.9508615008575</v>
+        <v>158.9495401544067</v>
       </c>
       <c r="E21" t="n">
-        <v>158.9519412250759</v>
+        <v>158.9495208646931</v>
       </c>
       <c r="F21" t="n">
-        <v>1.861037738393634</v>
+        <v>2.056544882094613</v>
       </c>
       <c r="G21" t="n">
-        <v>158.9518417548431</v>
+        <v>158.9502128095583</v>
       </c>
       <c r="H21" t="n">
-        <v>158.9503626922977</v>
+        <v>158.9510395012817</v>
       </c>
     </row>
     <row r="22">
@@ -5310,22 +5309,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>130.5251674374454</v>
+        <v>130.5243290533575</v>
       </c>
       <c r="D22" t="n">
-        <v>130.5228534227004</v>
+        <v>130.5234772605227</v>
       </c>
       <c r="E22" t="n">
-        <v>130.5246499712787</v>
+        <v>130.5243129654558</v>
       </c>
       <c r="F22" t="n">
-        <v>2.314014744996484</v>
+        <v>0.8517928348510395</v>
       </c>
       <c r="G22" t="n">
-        <v>130.5242236104748</v>
+        <v>130.5240397597787</v>
       </c>
       <c r="H22" t="n">
-        <v>130.5235386375541</v>
+        <v>130.5227940360481</v>
       </c>
     </row>
     <row r="23">
@@ -5340,22 +5339,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>130.5206922037729</v>
+        <v>130.5238285367664</v>
       </c>
       <c r="D23" t="n">
-        <v>130.5237331707401</v>
+        <v>130.5233509982065</v>
       </c>
       <c r="E23" t="n">
-        <v>130.5235713566731</v>
+        <v>130.5227935373156</v>
       </c>
       <c r="F23" t="n">
-        <v>3.040966967233771</v>
+        <v>1.034999450865826</v>
       </c>
       <c r="G23" t="n">
-        <v>130.522665577062</v>
+        <v>130.5233243574295</v>
       </c>
       <c r="H23" t="n">
-        <v>130.5235386375541</v>
+        <v>130.5227940360481</v>
       </c>
     </row>
     <row r="24">
@@ -5370,22 +5369,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>130.5221388520204</v>
+        <v>130.5207950353453</v>
       </c>
       <c r="D24" t="n">
-        <v>130.5248144870645</v>
+        <v>130.5225551090817</v>
       </c>
       <c r="E24" t="n">
-        <v>130.5242124598742</v>
+        <v>130.5215091852968</v>
       </c>
       <c r="F24" t="n">
-        <v>2.675635044056435</v>
+        <v>1.760073736392087</v>
       </c>
       <c r="G24" t="n">
-        <v>130.5237219329864</v>
+        <v>130.5216197765746</v>
       </c>
       <c r="H24" t="n">
-        <v>130.5235386375541</v>
+        <v>130.5227940360481</v>
       </c>
     </row>
     <row r="25">
@@ -5400,22 +5399,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>130.5232981960744</v>
+        <v>130.5214223606067</v>
       </c>
       <c r="D25" t="n">
-        <v>130.5228799306011</v>
+        <v>130.5231300414776</v>
       </c>
       <c r="E25" t="n">
-        <v>130.5244521624033</v>
+        <v>130.5220243491446</v>
       </c>
       <c r="F25" t="n">
-        <v>1.572231802157376</v>
+        <v>1.707680870850936</v>
       </c>
       <c r="G25" t="n">
-        <v>130.5235434296929</v>
+        <v>130.5221922504096</v>
       </c>
       <c r="H25" t="n">
-        <v>130.5235386375541</v>
+        <v>130.5227940360481</v>
       </c>
     </row>
     <row r="26">
@@ -5430,22 +5429,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>190.6018482176517</v>
+        <v>190.6033619928614</v>
       </c>
       <c r="D26" t="n">
-        <v>190.6035943718499</v>
+        <v>190.603542300522</v>
       </c>
       <c r="E26" t="n">
-        <v>190.6037105020723</v>
+        <v>190.6034407830836</v>
       </c>
       <c r="F26" t="n">
-        <v>1.862284420639071</v>
+        <v>0.1803076606279319</v>
       </c>
       <c r="G26" t="n">
-        <v>190.6030510305247</v>
+        <v>190.6034483588223</v>
       </c>
       <c r="H26" t="n">
-        <v>190.6032073476825</v>
+        <v>190.6029696408255</v>
       </c>
     </row>
     <row r="27">
@@ -5460,22 +5459,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>190.6041597506068</v>
+        <v>190.6020780263375</v>
       </c>
       <c r="D27" t="n">
-        <v>190.6034059406551</v>
+        <v>190.6030027263628</v>
       </c>
       <c r="E27" t="n">
-        <v>190.6030640860054</v>
+        <v>190.6035606943598</v>
       </c>
       <c r="F27" t="n">
-        <v>1.095664601336921</v>
+        <v>1.482668022362077</v>
       </c>
       <c r="G27" t="n">
-        <v>190.6035432590891</v>
+        <v>190.6028804823534</v>
       </c>
       <c r="H27" t="n">
-        <v>190.6032073476825</v>
+        <v>190.6029696408255</v>
       </c>
     </row>
     <row r="28">
@@ -5490,22 +5489,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>190.6021987382145</v>
+        <v>190.6028807027105</v>
       </c>
       <c r="D28" t="n">
-        <v>190.6036474746985</v>
+        <v>190.6031108270194</v>
       </c>
       <c r="E28" t="n">
-        <v>190.6039490960533</v>
+        <v>190.6027395064077</v>
       </c>
       <c r="F28" t="n">
-        <v>1.750357838773198</v>
+        <v>0.3713206116344736</v>
       </c>
       <c r="G28" t="n">
-        <v>190.6032651029888</v>
+        <v>190.6029103453792</v>
       </c>
       <c r="H28" t="n">
-        <v>190.6032073476825</v>
+        <v>190.6029696408255</v>
       </c>
     </row>
     <row r="29">
@@ -5520,22 +5519,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>190.6016171713055</v>
+        <v>190.6023849024092</v>
       </c>
       <c r="D29" t="n">
-        <v>190.6042950456744</v>
+        <v>190.6052813267357</v>
       </c>
       <c r="E29" t="n">
-        <v>190.6029977774031</v>
+        <v>190.6002519010967</v>
       </c>
       <c r="F29" t="n">
-        <v>2.677874368941957</v>
+        <v>5.029425639037299</v>
       </c>
       <c r="G29" t="n">
-        <v>190.6029699981276</v>
+        <v>190.6026393767472</v>
       </c>
       <c r="H29" t="n">
-        <v>190.6032073476825</v>
+        <v>190.6029696408255</v>
       </c>
     </row>
     <row r="30">
@@ -5550,22 +5549,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>123.7246081080256</v>
+        <v>123.7237130036129</v>
       </c>
       <c r="D30" t="n">
-        <v>123.7256112844503</v>
+        <v>123.7272885485738</v>
       </c>
       <c r="E30" t="n">
-        <v>123.7240669564045</v>
+        <v>123.7254275108354</v>
       </c>
       <c r="F30" t="n">
-        <v>1.544328045739007</v>
+        <v>3.575544960924049</v>
       </c>
       <c r="G30" t="n">
-        <v>123.7247621162935</v>
+        <v>123.7254763543407</v>
       </c>
       <c r="H30" t="n">
-        <v>123.725048852405</v>
+        <v>123.7256604726509</v>
       </c>
     </row>
     <row r="31">
@@ -5580,22 +5579,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>123.7243065963388</v>
+        <v>123.7265072350538</v>
       </c>
       <c r="D31" t="n">
-        <v>123.7241631573592</v>
+        <v>123.7273384964503</v>
       </c>
       <c r="E31" t="n">
-        <v>123.7270596049303</v>
+        <v>123.7250244817053</v>
       </c>
       <c r="F31" t="n">
-        <v>2.896447571089311</v>
+        <v>2.314014745010695</v>
       </c>
       <c r="G31" t="n">
-        <v>123.7251764528761</v>
+        <v>123.7262900710698</v>
       </c>
       <c r="H31" t="n">
-        <v>123.725048852405</v>
+        <v>123.7256604726509</v>
       </c>
     </row>
     <row r="32">
@@ -5610,22 +5609,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>123.7241788350343</v>
+        <v>123.7268210302835</v>
       </c>
       <c r="D32" t="n">
-        <v>123.7256136519886</v>
+        <v>123.7228632627777</v>
       </c>
       <c r="E32" t="n">
-        <v>123.7248047029098</v>
+        <v>123.725904229745</v>
       </c>
       <c r="F32" t="n">
-        <v>1.434816954315465</v>
+        <v>3.957767505809784</v>
       </c>
       <c r="G32" t="n">
-        <v>123.7248657299776</v>
+        <v>123.7251961742688</v>
       </c>
       <c r="H32" t="n">
-        <v>123.725048852405</v>
+        <v>123.7256604726509</v>
       </c>
     </row>
     <row r="33">
@@ -5640,22 +5639,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>123.7269105096342</v>
+        <v>123.725742415678</v>
       </c>
       <c r="D33" t="n">
-        <v>123.7247955144861</v>
+        <v>123.7243099110253</v>
       </c>
       <c r="E33" t="n">
-        <v>123.7244673072985</v>
+        <v>123.7269855460693</v>
       </c>
       <c r="F33" t="n">
-        <v>2.443202335712158</v>
+        <v>2.675635044056435</v>
       </c>
       <c r="G33" t="n">
-        <v>123.725391110473</v>
+        <v>123.7256792909242</v>
       </c>
       <c r="H33" t="n">
-        <v>123.725048852405</v>
+        <v>123.7256604726509</v>
       </c>
     </row>
     <row r="34">
@@ -5670,22 +5669,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>143.3880512972713</v>
+        <v>143.390194796317</v>
       </c>
       <c r="D34" t="n">
-        <v>143.3897099662358</v>
+        <v>143.3892805325172</v>
       </c>
       <c r="E34" t="n">
-        <v>143.3875307713984</v>
+        <v>143.3888622670439</v>
       </c>
       <c r="F34" t="n">
-        <v>2.179194837367504</v>
+        <v>1.332529273071259</v>
       </c>
       <c r="G34" t="n">
-        <v>143.3884306783018</v>
+        <v>143.3894458652927</v>
       </c>
       <c r="H34" t="n">
-        <v>143.3893463374762</v>
+        <v>143.388990578176</v>
       </c>
     </row>
     <row r="35">
@@ -5700,22 +5699,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>143.3891841318921</v>
+        <v>143.390434498846</v>
       </c>
       <c r="D35" t="n">
-        <v>143.3902212827306</v>
+        <v>143.3872839378559</v>
       </c>
       <c r="E35" t="n">
-        <v>143.3888155919738</v>
+        <v>143.3890300920541</v>
       </c>
       <c r="F35" t="n">
-        <v>1.405690756882905</v>
+        <v>3.150560990150097</v>
       </c>
       <c r="G35" t="n">
-        <v>143.3894070021988</v>
+        <v>143.388916176252</v>
       </c>
       <c r="H35" t="n">
-        <v>143.3893463374762</v>
+        <v>143.388990578176</v>
       </c>
     </row>
     <row r="36">
@@ -5730,22 +5729,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>143.3889775691416</v>
+        <v>143.3891462222765</v>
       </c>
       <c r="D36" t="n">
-        <v>143.3908203303691</v>
+        <v>143.3895954708109</v>
       </c>
       <c r="E36" t="n">
-        <v>143.3899819668453</v>
+        <v>143.3888416608593</v>
       </c>
       <c r="F36" t="n">
-        <v>1.842761227493384</v>
+        <v>0.7538099516466445</v>
       </c>
       <c r="G36" t="n">
-        <v>143.3899266221187</v>
+        <v>143.3891944513156</v>
       </c>
       <c r="H36" t="n">
-        <v>143.3893463374762</v>
+        <v>143.388990578176</v>
       </c>
     </row>
     <row r="37">
@@ -5760,22 +5759,22 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>143.3887059911678</v>
+        <v>143.3884998062096</v>
       </c>
       <c r="D37" t="n">
-        <v>143.3909693268721</v>
+        <v>143.3876344584187</v>
       </c>
       <c r="E37" t="n">
-        <v>143.3891878238169</v>
+        <v>143.3890831949027</v>
       </c>
       <c r="F37" t="n">
-        <v>2.263335704355995</v>
+        <v>1.448736484007895</v>
       </c>
       <c r="G37" t="n">
-        <v>143.3896210472856</v>
+        <v>143.3884058198437</v>
       </c>
       <c r="H37" t="n">
-        <v>143.3893463374762</v>
+        <v>143.388990578176</v>
       </c>
     </row>
     <row r="38">
@@ -5790,22 +5789,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>163.7453706838361</v>
+        <v>163.7441216549487</v>
       </c>
       <c r="D38" t="n">
-        <v>163.7431717498863</v>
+        <v>163.7417897302008</v>
       </c>
       <c r="E38" t="n">
-        <v>163.7413943651458</v>
+        <v>163.7444676045698</v>
       </c>
       <c r="F38" t="n">
-        <v>3.976318690348535</v>
+        <v>2.677874368941957</v>
       </c>
       <c r="G38" t="n">
-        <v>163.7433122662894</v>
+        <v>163.7434596632397</v>
       </c>
       <c r="H38" t="n">
-        <v>163.7439704200798</v>
+        <v>163.7434618707985</v>
       </c>
     </row>
     <row r="39">
@@ -5820,22 +5819,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>163.7451469107774</v>
+        <v>163.7431703362984</v>
       </c>
       <c r="D39" t="n">
-        <v>163.7438605625022</v>
+        <v>163.7431562241547</v>
       </c>
       <c r="E39" t="n">
-        <v>163.7450658157852</v>
+        <v>163.7441594005793</v>
       </c>
       <c r="F39" t="n">
-        <v>1.286348275158389</v>
+        <v>1.00317642460368</v>
       </c>
       <c r="G39" t="n">
-        <v>163.7446910963549</v>
+        <v>163.7434953203442</v>
       </c>
       <c r="H39" t="n">
-        <v>163.7439704200798</v>
+        <v>163.7434618707985</v>
       </c>
     </row>
     <row r="40">
@@ -5850,22 +5849,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>163.7444637748574</v>
+        <v>163.7426150725336</v>
       </c>
       <c r="D40" t="n">
-        <v>163.7426782472691</v>
+        <v>163.7428547124679</v>
       </c>
       <c r="E40" t="n">
-        <v>163.7446731297792</v>
+        <v>163.7427112734883</v>
       </c>
       <c r="F40" t="n">
-        <v>1.994882510132356</v>
+        <v>0.2396399343069788</v>
       </c>
       <c r="G40" t="n">
-        <v>163.7439383839686</v>
+        <v>163.7427270194966</v>
       </c>
       <c r="H40" t="n">
-        <v>163.7439704200798</v>
+        <v>163.7434618707985</v>
       </c>
     </row>
     <row r="41">
@@ -5880,22 +5879,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>163.7435515574292</v>
+        <v>163.7456077210594</v>
       </c>
       <c r="D41" t="n">
-        <v>163.7450759585222</v>
+        <v>163.7427269511634</v>
       </c>
       <c r="E41" t="n">
-        <v>163.7431922851673</v>
+        <v>163.7441617681177</v>
       </c>
       <c r="F41" t="n">
-        <v>1.883673354882376</v>
+        <v>2.88076989596675</v>
       </c>
       <c r="G41" t="n">
-        <v>163.7439399337063</v>
+        <v>163.7441654801135</v>
       </c>
       <c r="H41" t="n">
-        <v>163.7439704200798</v>
+        <v>163.7434618707985</v>
       </c>
     </row>
     <row r="42">
@@ -5910,22 +5909,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>135.1763742967996</v>
+        <v>135.174353568515</v>
       </c>
       <c r="D42" t="n">
-        <v>135.1742464200226</v>
+        <v>135.1764593752393</v>
       </c>
       <c r="E42" t="n">
-        <v>135.1748926958607</v>
+        <v>135.1743443800912</v>
       </c>
       <c r="F42" t="n">
-        <v>2.127876776967241</v>
+        <v>2.114995148104981</v>
       </c>
       <c r="G42" t="n">
-        <v>135.175171137561</v>
+        <v>135.1750524412818</v>
       </c>
       <c r="H42" t="n">
-        <v>135.1748963079945</v>
+        <v>135.1748654285916</v>
       </c>
     </row>
     <row r="43">
@@ -5940,22 +5939,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>135.1767249732778</v>
+        <v>135.1740161729037</v>
       </c>
       <c r="D43" t="n">
-        <v>135.1754842561052</v>
+        <v>135.1737888854385</v>
       </c>
       <c r="E43" t="n">
-        <v>135.1752474764103</v>
+        <v>135.175447554403</v>
       </c>
       <c r="F43" t="n">
-        <v>1.47749686749421</v>
+        <v>1.658668964495291</v>
       </c>
       <c r="G43" t="n">
-        <v>135.1758189019311</v>
+        <v>135.1744175375817</v>
       </c>
       <c r="H43" t="n">
-        <v>135.1748963079945</v>
+        <v>135.1748654285916</v>
       </c>
     </row>
     <row r="44">
@@ -5970,22 +5969,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>135.1748391056427</v>
+        <v>135.1732683595656</v>
       </c>
       <c r="D44" t="n">
-        <v>135.1728989099157</v>
+        <v>135.1749217200593</v>
       </c>
       <c r="E44" t="n">
-        <v>135.1756070628868</v>
+        <v>135.1759588708978</v>
       </c>
       <c r="F44" t="n">
-        <v>2.708152971109712</v>
+        <v>2.690511332218648</v>
       </c>
       <c r="G44" t="n">
-        <v>135.1744483594817</v>
+        <v>135.1747163168409</v>
       </c>
       <c r="H44" t="n">
-        <v>135.1748963079945</v>
+        <v>135.1748654285916</v>
       </c>
     </row>
     <row r="45">
@@ -6000,22 +5999,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>135.1747895315157</v>
+        <v>135.1745531801409</v>
       </c>
       <c r="D45" t="n">
-        <v>135.1736196998751</v>
+        <v>135.1747151573088</v>
       </c>
       <c r="E45" t="n">
-        <v>135.1740312676222</v>
+        <v>135.1765579185363</v>
       </c>
       <c r="F45" t="n">
-        <v>1.169831640623897</v>
+        <v>2.004738395356753</v>
       </c>
       <c r="G45" t="n">
-        <v>135.1741468330043</v>
+        <v>135.175275418662</v>
       </c>
       <c r="H45" t="n">
-        <v>135.1748963079945</v>
+        <v>135.1748654285916</v>
       </c>
     </row>
     <row r="46">
@@ -6030,22 +6029,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>195.8857721935496</v>
+        <v>195.8874557181627</v>
       </c>
       <c r="D46" t="n">
-        <v>195.8854997745937</v>
+        <v>195.8861797424851</v>
       </c>
       <c r="E46" t="n">
-        <v>195.8874196756805</v>
+        <v>195.8884430781895</v>
       </c>
       <c r="F46" t="n">
-        <v>1.919901086864684</v>
+        <v>2.263335704355995</v>
       </c>
       <c r="G46" t="n">
-        <v>195.8862305479413</v>
+        <v>195.8873595129457</v>
       </c>
       <c r="H46" t="n">
-        <v>195.8860712044878</v>
+        <v>195.8868156270867</v>
       </c>
     </row>
     <row r="47">
@@ -6060,22 +6059,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>195.884792993728</v>
+        <v>195.8866615751343</v>
       </c>
       <c r="D47" t="n">
-        <v>195.8863768620301</v>
+        <v>195.8881075964623</v>
       </c>
       <c r="E47" t="n">
-        <v>195.8879333548178</v>
+        <v>195.8859086625125</v>
       </c>
       <c r="F47" t="n">
-        <v>3.140361089833732</v>
+        <v>2.19893394984183</v>
       </c>
       <c r="G47" t="n">
-        <v>195.8863677368586</v>
+        <v>195.8868926113697</v>
       </c>
       <c r="H47" t="n">
-        <v>195.8860712044878</v>
+        <v>195.8868156270867</v>
       </c>
     </row>
     <row r="48">
@@ -6090,22 +6089,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>195.8859544757707</v>
+        <v>195.884131277772</v>
       </c>
       <c r="D48" t="n">
-        <v>195.8871835144101</v>
+        <v>195.8878838234036</v>
       </c>
       <c r="E48" t="n">
-        <v>195.8845840876256</v>
+        <v>195.8865974751284</v>
       </c>
       <c r="F48" t="n">
-        <v>2.599426784513525</v>
+        <v>3.752545631613202</v>
       </c>
       <c r="G48" t="n">
-        <v>195.8859073592688</v>
+        <v>195.8862041921013</v>
       </c>
       <c r="H48" t="n">
-        <v>195.8860712044878</v>
+        <v>195.8868156270867</v>
       </c>
     </row>
     <row r="49">
@@ -6120,22 +6119,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>195.8874769124374</v>
+        <v>195.8878027284113</v>
       </c>
       <c r="D49" t="n">
-        <v>195.8848870868244</v>
+        <v>195.8872006874836</v>
       </c>
       <c r="E49" t="n">
-        <v>195.8849735223858</v>
+        <v>195.8854151598953</v>
       </c>
       <c r="F49" t="n">
-        <v>2.589825612943741</v>
+        <v>2.387568516041938</v>
       </c>
       <c r="G49" t="n">
-        <v>195.8857791738825</v>
+        <v>195.8868061919301</v>
       </c>
       <c r="H49" t="n">
-        <v>195.8860712044878</v>
+        <v>195.8868156270867</v>
       </c>
     </row>
     <row r="50">
@@ -6150,22 +6149,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>196.550629706282</v>
+        <v>196.5516013950617</v>
       </c>
       <c r="D50" t="n">
-        <v>196.5512295057092</v>
+        <v>196.5504798227117</v>
       </c>
       <c r="E50" t="n">
-        <v>196.5481004921476</v>
+        <v>196.5520042238047</v>
       </c>
       <c r="F50" t="n">
-        <v>3.129013561618876</v>
+        <v>1.524401093007555</v>
       </c>
       <c r="G50" t="n">
-        <v>196.5499865680463</v>
+        <v>196.5513618138594</v>
       </c>
       <c r="H50" t="n">
-        <v>196.5505767612925</v>
+        <v>196.5510278543762</v>
       </c>
     </row>
     <row r="51">
@@ -6180,22 +6179,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>196.5518961539915</v>
+        <v>196.5501205504498</v>
       </c>
       <c r="D51" t="n">
-        <v>196.550046456245</v>
+        <v>196.552301812606</v>
       </c>
       <c r="E51" t="n">
-        <v>196.5530802667235</v>
+        <v>196.550173935829</v>
       </c>
       <c r="F51" t="n">
-        <v>3.033810478569876</v>
+        <v>2.181262156199182</v>
       </c>
       <c r="G51" t="n">
-        <v>196.55167429232</v>
+        <v>196.5508654329616</v>
       </c>
       <c r="H51" t="n">
-        <v>196.5505767612925</v>
+        <v>196.5510278543762</v>
       </c>
     </row>
     <row r="52">
@@ -6210,22 +6209,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>196.5493584290302</v>
+        <v>196.5508202116671</v>
       </c>
       <c r="D52" t="n">
-        <v>196.5500984005804</v>
+        <v>196.5526524890842</v>
       </c>
       <c r="E52" t="n">
-        <v>196.5508439452742</v>
+        <v>196.5514117719116</v>
       </c>
       <c r="F52" t="n">
-        <v>1.48551624403126</v>
+        <v>1.832277417094019</v>
       </c>
       <c r="G52" t="n">
-        <v>196.5501002582949</v>
+        <v>196.5516281575543</v>
       </c>
       <c r="H52" t="n">
-        <v>196.5505767612925</v>
+        <v>196.5510278543762</v>
       </c>
     </row>
     <row r="53">
@@ -6240,22 +6239,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>196.54891156782</v>
+        <v>196.5511749922167</v>
       </c>
       <c r="D53" t="n">
-        <v>196.5512384462116</v>
+        <v>196.5507666214491</v>
       </c>
       <c r="E53" t="n">
-        <v>196.5514877654948</v>
+        <v>196.5488264257221</v>
       </c>
       <c r="F53" t="n">
-        <v>2.576197674756031</v>
+        <v>2.34856649464632</v>
       </c>
       <c r="G53" t="n">
-        <v>196.5505459265088</v>
+        <v>196.5502560131293</v>
       </c>
       <c r="H53" t="n">
-        <v>196.5505767612925</v>
+        <v>196.5510278543762</v>
       </c>
     </row>
   </sheetData>
@@ -6273,7 +6272,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -6369,12 +6368,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>168°21'49.7"</t>
+          <t>168°21'47.6"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -6403,33 +6402,33 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57°51'29.7"</t>
+          <t>57°51'26.8"</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>171.329761760525</v>
+        <v>171.3294933455056</v>
       </c>
       <c r="G3" t="n">
-        <v>91.15011651996439</v>
+        <v>91.15201201463836</v>
       </c>
       <c r="H3" t="n">
-        <v>145.0708224396456</v>
+        <v>145.0693144524743</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>91.15188111184443</v>
+        <v>91.14985713063325</v>
       </c>
       <c r="L3" t="n">
-        <v>145.0688016173075</v>
+        <v>145.0712518340842</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -6442,17 +6441,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>165°41'16.5"</t>
+          <t>165°41'17.0"</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>165°41'16.0"</t>
+          <t>165°41'17.2"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -6464,10 +6463,10 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>192.7389811118445</v>
+        <v>192.7369571306332</v>
       </c>
       <c r="N4" t="n">
-        <v>416.6936016173074</v>
+        <v>416.6960518340842</v>
       </c>
     </row>
     <row r="5">
@@ -6481,33 +6480,33 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>43°32'46.2"</t>
+          <t>43°32'43.8"</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>125.0647150134671</v>
+        <v>125.0649859305766</v>
       </c>
       <c r="G5" t="n">
-        <v>90.64933796008401</v>
+        <v>90.65055137922391</v>
       </c>
       <c r="H5" t="n">
-        <v>86.16194327426824</v>
+        <v>86.1610598847183</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>90.65062605024607</v>
+        <v>90.6489783836321</v>
       </c>
       <c r="L5" t="n">
-        <v>86.1604681448616</v>
+        <v>86.16247411059993</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -6520,17 +6519,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>204°35'21.4"</t>
+          <t>204°35'20.4"</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>204°35'20.9"</t>
+          <t>204°35'20.6"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -6542,10 +6541,10 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>283.3896071620906</v>
+        <v>283.3859355142653</v>
       </c>
       <c r="N6" t="n">
-        <v>502.854069762169</v>
+        <v>502.8585259446841</v>
       </c>
     </row>
     <row r="7">
@@ -6559,33 +6558,33 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>68°08'07.6"</t>
+          <t>68°08'04.2"</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>134.9521831598235</v>
+        <v>134.9520033228584</v>
       </c>
       <c r="G7" t="n">
-        <v>50.25803568029852</v>
+        <v>50.26005814835942</v>
       </c>
       <c r="H7" t="n">
-        <v>125.2446469481247</v>
+        <v>125.2436415782307</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>50.25942560534219</v>
+        <v>50.25836079953908</v>
       </c>
       <c r="L7" t="n">
-        <v>125.2430551967354</v>
+        <v>125.2451676057952</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -6598,17 +6597,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>136°00'13.8"</t>
+          <t>136°00'14.0"</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>136°00'13.3"</t>
+          <t>136°00'14.3"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -6620,10 +6619,10 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>333.6490327674327</v>
+        <v>333.6442963138044</v>
       </c>
       <c r="N8" t="n">
-        <v>628.0971249589045</v>
+        <v>628.1036935504793</v>
       </c>
     </row>
     <row r="9">
@@ -6637,33 +6636,33 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24°08'21.4"</t>
+          <t>24°08'18.2"</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>149.5849427858228</v>
+        <v>149.5850999747892</v>
       </c>
       <c r="G9" t="n">
-        <v>136.5043345567964</v>
+        <v>136.5054299663758</v>
       </c>
       <c r="H9" t="n">
-        <v>61.17370150190428</v>
+        <v>61.17164150292636</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>136.505875190325</v>
+        <v>136.5035485708668</v>
       </c>
       <c r="L9" t="n">
-        <v>61.17193715815737</v>
+        <v>61.17333300049713</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -6676,17 +6675,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>177°58'47.0"</t>
+          <t>177°58'47.4"</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>177°58'46.5"</t>
+          <t>177°58'47.7"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -6698,10 +6697,10 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>470.1549079577577</v>
+        <v>470.1478448846713</v>
       </c>
       <c r="N10" t="n">
-        <v>689.2690621170618</v>
+        <v>689.2770265509764</v>
       </c>
     </row>
     <row r="11">
@@ -6715,33 +6714,33 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22°07'08.4"</t>
+          <t>22°07'05.7"</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>158.9503626922977</v>
+        <v>158.9510395012816</v>
       </c>
       <c r="G11" t="n">
-        <v>147.2522124430969</v>
+        <v>147.2536424805108</v>
       </c>
       <c r="H11" t="n">
-        <v>59.84984319633632</v>
+        <v>59.84812223253043</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>147.2538495347292</v>
+        <v>147.2516432855915</v>
       </c>
       <c r="L11" t="n">
-        <v>59.84796838812861</v>
+        <v>59.84991963947293</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -6754,17 +6753,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>188°23'24.0"</t>
+          <t>188°23'22.7"</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>188°23'23.5"</t>
+          <t>188°23'22.9"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -6776,10 +6775,10 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>617.4087574924869</v>
+        <v>617.3994881702628</v>
       </c>
       <c r="N12" t="n">
-        <v>749.1170305051904</v>
+        <v>749.1269461904493</v>
       </c>
     </row>
     <row r="13">
@@ -6793,33 +6792,33 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30°30'32.5"</t>
+          <t>30°30'28.3"</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>130.5235386375541</v>
+        <v>130.5227940360481</v>
       </c>
       <c r="G13" t="n">
-        <v>112.4524525741314</v>
+        <v>112.4531460103301</v>
       </c>
       <c r="H13" t="n">
-        <v>66.26341410259359</v>
+        <v>66.26077056113975</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>112.453796886842</v>
+        <v>112.4515043695613</v>
       </c>
       <c r="L13" t="n">
-        <v>66.26187458675108</v>
+        <v>66.26224650352358</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -6832,17 +6831,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>189°24'37.7"</t>
+          <t>189°24'37.1"</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>189°24'37.2"</t>
+          <t>189°24'37.4"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -6854,10 +6853,10 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>729.8625543793288</v>
+        <v>729.8509925398241</v>
       </c>
       <c r="N14" t="n">
-        <v>815.3789050919415</v>
+        <v>815.3891926939729</v>
       </c>
     </row>
     <row r="15">
@@ -6871,33 +6870,33 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>39°55'10.1"</t>
+          <t>39°55'05.4"</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>190.6032073476825</v>
+        <v>190.6029696408255</v>
       </c>
       <c r="G15" t="n">
-        <v>146.1825572364172</v>
+        <v>146.1851623068641</v>
       </c>
       <c r="H15" t="n">
-        <v>122.3120705860434</v>
+        <v>122.3085866046095</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>146.1845203330126</v>
+        <v>146.1827650121393</v>
       </c>
       <c r="L15" t="n">
-        <v>122.3098224347873</v>
+        <v>122.3107419293055</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -6910,17 +6909,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>182°02'14.5"</t>
+          <t>182°02'10.4"</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>182°02'13.9"</t>
+          <t>182°02'10.6"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -6932,10 +6931,10 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>876.0470747123413</v>
+        <v>876.0337575519634</v>
       </c>
       <c r="N16" t="n">
-        <v>937.6887275267288</v>
+        <v>937.6999346232783</v>
       </c>
     </row>
     <row r="17">
@@ -6949,33 +6948,33 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41°57'24.6"</t>
+          <t>41°57'15.9"</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>123.725048852405</v>
+        <v>123.7256604726508</v>
       </c>
       <c r="G17" t="n">
-        <v>92.00795949210521</v>
+        <v>92.01193481762328</v>
       </c>
       <c r="H17" t="n">
-        <v>82.71894041650398</v>
+        <v>82.71543332722811</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>92.00923378452423</v>
+        <v>92.01037866729816</v>
       </c>
       <c r="L17" t="n">
-        <v>82.71748108836431</v>
+        <v>82.71683240811363</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -6988,17 +6987,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>207°10'04.1"</t>
+          <t>207°10'03.3"</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>207°10'03.6"</t>
+          <t>207°10'03.5"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -7010,10 +7009,10 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>968.0563084968655</v>
+        <v>968.0441362192615</v>
       </c>
       <c r="N18" t="n">
-        <v>1020.406208615093</v>
+        <v>1020.416767031392</v>
       </c>
     </row>
     <row r="19">
@@ -7027,33 +7026,33 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>69°07'28.8"</t>
+          <t>69°07'19.2"</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>143.3893463374762</v>
+        <v>143.388990578176</v>
       </c>
       <c r="G19" t="n">
-        <v>51.09476927417946</v>
+        <v>51.10087756085862</v>
       </c>
       <c r="H19" t="n">
-        <v>133.9769726330129</v>
+        <v>133.974262198149</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>51.09624609684957</v>
+        <v>51.09907409645636</v>
       </c>
       <c r="L19" t="n">
-        <v>133.9752813658848</v>
+        <v>133.9758836305596</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -7066,17 +7065,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>151°14'50.2"</t>
+          <t>151°14'49.0"</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>151°14'49.7"</t>
+          <t>151°14'49.3"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -7088,10 +7087,10 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>1019.152554593715</v>
+        <v>1019.143210315718</v>
       </c>
       <c r="N20" t="n">
-        <v>1154.381489980978</v>
+        <v>1154.392650661952</v>
       </c>
     </row>
     <row r="21">
@@ -7105,33 +7104,33 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40°22'19.0"</t>
+          <t>40°22'08.2"</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>163.7439704200798</v>
+        <v>163.7434618707985</v>
       </c>
       <c r="G21" t="n">
-        <v>124.7492510184455</v>
+        <v>124.7544302343493</v>
       </c>
       <c r="H21" t="n">
-        <v>106.0646605579297</v>
+        <v>106.0577835066174</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>124.7509374813089</v>
+        <v>124.7523707630928</v>
       </c>
       <c r="L21" t="n">
-        <v>106.0627292094602</v>
+        <v>106.059635105928</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -7144,17 +7143,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>190°00'04.8"</t>
+          <t>190°00'03.5"</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>190°00'04.3"</t>
+          <t>190°00'03.7"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -7166,10 +7165,10 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>1143.903492075024</v>
+        <v>1143.895581078811</v>
       </c>
       <c r="N22" t="n">
-        <v>1260.444219190438</v>
+        <v>1260.45228576788</v>
       </c>
     </row>
     <row r="23">
@@ -7183,33 +7182,33 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>50°22'23.8"</t>
+          <t>50°22'11.7"</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>135.1748963079945</v>
+        <v>135.1748654285916</v>
       </c>
       <c r="G23" t="n">
-        <v>86.21228062296397</v>
+        <v>86.21839255519777</v>
       </c>
       <c r="H23" t="n">
-        <v>104.1138572028929</v>
+        <v>104.1087557741215</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>86.21367284181702</v>
+        <v>86.21669240334582</v>
       </c>
       <c r="L23" t="n">
-        <v>104.112262824618</v>
+        <v>104.1102843217946</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -7222,17 +7221,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>152°59'34.7"</t>
+          <t>152°59'35.5"</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>152°59'34.2"</t>
+          <t>152°59'35.8"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -7244,10 +7243,10 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>1230.117164916841</v>
+        <v>1230.112273482157</v>
       </c>
       <c r="N24" t="n">
-        <v>1364.556482015056</v>
+        <v>1364.562570089674</v>
       </c>
     </row>
     <row r="25">
@@ -7261,33 +7260,33 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23°21'58.5"</t>
+          <t>23°21'47.1"</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>195.8860712044878</v>
+        <v>195.8868156270867</v>
       </c>
       <c r="G25" t="n">
-        <v>179.8211397594116</v>
+        <v>179.8261045269858</v>
       </c>
       <c r="H25" t="n">
-        <v>77.68983580595227</v>
+        <v>77.68022056591911</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>179.8231572662773</v>
+        <v>179.8236407750797</v>
       </c>
       <c r="L25" t="n">
-        <v>77.68752534369317</v>
+        <v>77.68243563996617</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -7300,17 +7299,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>212°17'05.6"</t>
+          <t>212°17'06.0"</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>212°17'05.1"</t>
+          <t>212°17'06.3"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -7322,10 +7321,10 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>1409.940322183118</v>
+        <v>1409.935914257236</v>
       </c>
       <c r="N26" t="n">
-        <v>1442.24400735875</v>
+        <v>1442.24500572964</v>
       </c>
     </row>
     <row r="27">
@@ -7339,33 +7338,33 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>55°39'04.2"</t>
+          <t>55°38'53.2"</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>196.5505767612925</v>
+        <v>196.5510278543762</v>
       </c>
       <c r="G27" t="n">
-        <v>110.8997534660145</v>
+        <v>110.9086578487502</v>
       </c>
       <c r="H27" t="n">
-        <v>162.2756109413055</v>
+        <v>162.2700716854486</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>110.9017778168816</v>
+        <v>110.906185742764</v>
       </c>
       <c r="L27" t="n">
-        <v>162.2732926412507</v>
+        <v>162.2722942703599</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -7379,12 +7378,12 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>197°25'07.7"</t>
+          <t>197°25'08.8"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -7413,7 +7412,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>73°04'12.4"</t>
+          <t>73°04'01.7"</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -7443,7 +7442,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7.082442139188444</v>
+        <v>-3.616237120651302</v>
       </c>
     </row>
     <row r="33">
@@ -7453,7 +7452,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.02079939609097892</v>
+        <v>0.02539985006728784</v>
       </c>
     </row>
     <row r="34">
@@ -7463,7 +7462,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.02381960651337067</v>
+        <v>-0.02283612588712458</v>
       </c>
     </row>
     <row r="35">
@@ -7473,7 +7472,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.03162259527934479</v>
+        <v>0.03415612725373449</v>
       </c>
     </row>
     <row r="36">
@@ -7483,7 +7482,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2019.478621280909</v>
+        <v>2019.479207583565</v>
       </c>
     </row>
   </sheetData>
